--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 лгрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/07,26/02,07,26 ПОКОМ КИ/дв 02,07,26 лгрсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\07,26\02,07,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7892243-876D-4674-AD1C-DF54A0EB30A4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DA5BD3-3F99-4420-AFB6-2C45D2F86554}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1349,7 +1349,8 @@
     <col min="24" max="30" width="6.85546875" customWidth="1"/>
     <col min="31" max="31" width="36.28515625" customWidth="1"/>
     <col min="32" max="33" width="7" customWidth="1"/>
-    <col min="34" max="51" width="3" customWidth="1"/>
+    <col min="34" max="34" width="8" customWidth="1"/>
+    <col min="35" max="51" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
@@ -1765,7 +1766,10 @@
         <f>SUM(AG6:AG497)</f>
         <v>8807</v>
       </c>
-      <c r="AH5" s="1"/>
+      <c r="AH5" s="4">
+        <f>SUM(AH6:AH497)</f>
+        <v>8187.4825999999985</v>
+      </c>
       <c r="AI5" s="1"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
@@ -1884,7 +1888,10 @@
         <f>ROUND(G6*U6,0)</f>
         <v>824</v>
       </c>
-      <c r="AH6" s="1"/>
+      <c r="AH6" s="1">
+        <f>Q6*G6</f>
+        <v>649.26400000000001</v>
+      </c>
       <c r="AI6" s="1"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
@@ -2003,7 +2010,10 @@
         <f t="shared" ref="AG7:AG70" si="11">ROUND(G7*U7,0)</f>
         <v>610</v>
       </c>
-      <c r="AH7" s="1"/>
+      <c r="AH7" s="1">
+        <f t="shared" ref="AH7:AH70" si="12">Q7*G7</f>
+        <v>245.24720000000002</v>
+      </c>
       <c r="AI7" s="1"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -2122,7 +2132,10 @@
         <f t="shared" si="11"/>
         <v>443</v>
       </c>
-      <c r="AH8" s="1"/>
+      <c r="AH8" s="1">
+        <f t="shared" si="12"/>
+        <v>252.57440000000003</v>
+      </c>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="1"/>
@@ -2192,7 +2205,7 @@
         <v>338.86400000000026</v>
       </c>
       <c r="S9" s="5">
-        <f t="shared" ref="S9:S70" si="12">R9</f>
+        <f t="shared" ref="S9:S70" si="13">R9</f>
         <v>338.86400000000026</v>
       </c>
       <c r="T9" s="5">
@@ -2238,7 +2251,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH9" s="1"/>
+      <c r="AH9" s="1">
+        <f t="shared" si="12"/>
+        <v>51.930000000000007</v>
+      </c>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="1"/>
@@ -2308,7 +2324,7 @@
         <v>635.40400000000022</v>
       </c>
       <c r="S10" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>635.40400000000022</v>
       </c>
       <c r="T10" s="5">
@@ -2357,7 +2373,10 @@
         <f t="shared" si="11"/>
         <v>129</v>
       </c>
-      <c r="AH10" s="1"/>
+      <c r="AH10" s="1">
+        <f t="shared" si="12"/>
+        <v>89.460000000000008</v>
+      </c>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
       <c r="AK10" s="1"/>
@@ -2424,7 +2443,7 @@
       </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T11" s="5"/>
@@ -2467,7 +2486,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="1"/>
+      <c r="AH11" s="1">
+        <f t="shared" si="12"/>
+        <v>3.0940000000000003</v>
+      </c>
       <c r="AI11" s="1"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
@@ -2524,7 +2546,7 @@
       </c>
       <c r="R12" s="11"/>
       <c r="S12" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T12" s="11"/>
@@ -2567,7 +2589,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="1"/>
+      <c r="AH12" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1"/>
       <c r="AK12" s="1"/>
@@ -2631,15 +2656,15 @@
         <v>11.6</v>
       </c>
       <c r="R13" s="5">
-        <f t="shared" ref="R13:R14" si="13">12*Q13-P13-O13-F13</f>
+        <f t="shared" ref="R13:R14" si="14">12*Q13-P13-O13-F13</f>
         <v>10.199999999999989</v>
       </c>
       <c r="S13" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.199999999999989</v>
       </c>
       <c r="T13" s="5">
-        <f t="shared" ref="T13:T14" si="14">S13-U13</f>
+        <f t="shared" ref="T13:T14" si="15">S13-U13</f>
         <v>10.199999999999989</v>
       </c>
       <c r="U13" s="5"/>
@@ -2681,7 +2706,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH13" s="1"/>
+      <c r="AH13" s="1">
+        <f t="shared" si="12"/>
+        <v>3.48</v>
+      </c>
       <c r="AI13" s="1"/>
       <c r="AJ13" s="1"/>
       <c r="AK13" s="1"/>
@@ -2747,15 +2775,15 @@
         <v>51</v>
       </c>
       <c r="R14" s="5">
+        <f t="shared" si="14"/>
+        <v>233.01600000000002</v>
+      </c>
+      <c r="S14" s="5">
         <f t="shared" si="13"/>
         <v>233.01600000000002</v>
       </c>
-      <c r="S14" s="5">
-        <f t="shared" si="12"/>
-        <v>233.01600000000002</v>
-      </c>
       <c r="T14" s="5">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>233.01600000000002</v>
       </c>
       <c r="U14" s="5"/>
@@ -2797,7 +2825,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="1"/>
+      <c r="AH14" s="1">
+        <f t="shared" si="12"/>
+        <v>8.67</v>
+      </c>
       <c r="AI14" s="1"/>
       <c r="AJ14" s="1"/>
       <c r="AK14" s="1"/>
@@ -2858,7 +2889,7 @@
       </c>
       <c r="R15" s="11"/>
       <c r="S15" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T15" s="11"/>
@@ -2901,7 +2932,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="1"/>
+      <c r="AH15" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
       <c r="AK15" s="1"/>
@@ -2967,19 +3001,19 @@
         <v>225.66140000000001</v>
       </c>
       <c r="R16" s="5">
-        <f t="shared" ref="R16:R18" si="15">12*Q16-P16-O16-F16</f>
+        <f t="shared" ref="R16:R18" si="16">12*Q16-P16-O16-F16</f>
         <v>391.0901920000008</v>
       </c>
       <c r="S16" s="5">
-        <f t="shared" ref="S16:S17" si="16">R16+Q16*$S$1</f>
+        <f t="shared" ref="S16:S17" si="17">R16+Q16*$S$1</f>
         <v>538.44708620000085</v>
       </c>
       <c r="T16" s="5">
-        <f t="shared" ref="T16:T18" si="17">S16-U16</f>
+        <f t="shared" ref="T16:T18" si="18">S16-U16</f>
         <v>295.90335367747798</v>
       </c>
       <c r="U16" s="5">
-        <f t="shared" ref="U16:U17" si="18">S16/$U$1</f>
+        <f t="shared" ref="U16:U17" si="19">S16/$U$1</f>
         <v>242.54373252252287</v>
       </c>
       <c r="V16" s="1">
@@ -3020,7 +3054,10 @@
         <f t="shared" si="11"/>
         <v>243</v>
       </c>
-      <c r="AH16" s="1"/>
+      <c r="AH16" s="1">
+        <f t="shared" si="12"/>
+        <v>225.66140000000001</v>
+      </c>
       <c r="AI16" s="1"/>
       <c r="AJ16" s="1"/>
       <c r="AK16" s="1"/>
@@ -3086,19 +3123,19 @@
         <v>727.9</v>
       </c>
       <c r="R17" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>697.62018399999852</v>
       </c>
       <c r="S17" s="5">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>1172.9388839999986</v>
       </c>
       <c r="T17" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>644.58803535135064</v>
       </c>
       <c r="U17" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>528.35084864864791</v>
       </c>
       <c r="V17" s="1">
@@ -3139,7 +3176,10 @@
         <f t="shared" si="11"/>
         <v>528</v>
       </c>
-      <c r="AH17" s="1"/>
+      <c r="AH17" s="1">
+        <f t="shared" si="12"/>
+        <v>727.9</v>
+      </c>
       <c r="AI17" s="1"/>
       <c r="AJ17" s="1"/>
       <c r="AK17" s="1"/>
@@ -3205,15 +3245,15 @@
         <v>18.616199999999999</v>
       </c>
       <c r="R18" s="5">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>30.716003999999941</v>
       </c>
       <c r="S18" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>30.716003999999941</v>
       </c>
       <c r="T18" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>30.716003999999941</v>
       </c>
       <c r="U18" s="5"/>
@@ -3255,7 +3295,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="1"/>
+      <c r="AH18" s="1">
+        <f t="shared" si="12"/>
+        <v>18.616199999999999</v>
+      </c>
       <c r="AI18" s="1"/>
       <c r="AJ18" s="1"/>
       <c r="AK18" s="1"/>
@@ -3320,7 +3363,7 @@
       </c>
       <c r="R19" s="11"/>
       <c r="S19" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T19" s="11"/>
@@ -3365,7 +3408,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="1"/>
+      <c r="AH19" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AI19" s="1"/>
       <c r="AJ19" s="1"/>
       <c r="AK19" s="1"/>
@@ -3431,11 +3477,11 @@
         <v>16.781600000000001</v>
       </c>
       <c r="R20" s="5">
-        <f t="shared" ref="R20:R25" si="19">12*Q20-P20-O20-F20</f>
+        <f t="shared" ref="R20:R25" si="20">12*Q20-P20-O20-F20</f>
         <v>75.495468000000045</v>
       </c>
       <c r="S20" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>75.495468000000045</v>
       </c>
       <c r="T20" s="5">
@@ -3481,7 +3527,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="1"/>
+      <c r="AH20" s="1">
+        <f t="shared" si="12"/>
+        <v>16.781600000000001</v>
+      </c>
       <c r="AI20" s="1"/>
       <c r="AJ20" s="1"/>
       <c r="AK20" s="1"/>
@@ -3546,7 +3595,7 @@
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T21" s="5"/>
@@ -3589,7 +3638,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="1"/>
+      <c r="AH21" s="1">
+        <f t="shared" si="12"/>
+        <v>1.2132000000000001</v>
+      </c>
       <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
@@ -3655,7 +3707,7 @@
         <v>282.6694</v>
       </c>
       <c r="R22" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1300.7351200000003</v>
       </c>
       <c r="S22" s="5">
@@ -3663,7 +3715,7 @@
         <v>1485.3182382000002</v>
       </c>
       <c r="T22" s="5">
-        <f t="shared" ref="T22:T25" si="20">S22-U22</f>
+        <f t="shared" ref="T22:T25" si="21">S22-U22</f>
         <v>816.25596874054077</v>
       </c>
       <c r="U22" s="5">
@@ -3708,7 +3760,10 @@
         <f t="shared" si="11"/>
         <v>669</v>
       </c>
-      <c r="AH22" s="1"/>
+      <c r="AH22" s="1">
+        <f t="shared" si="12"/>
+        <v>282.6694</v>
+      </c>
       <c r="AI22" s="1"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
@@ -3772,15 +3827,15 @@
         <v>32.327999999999996</v>
       </c>
       <c r="R23" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>99.099999999999909</v>
       </c>
       <c r="S23" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>99.099999999999909</v>
       </c>
       <c r="T23" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>99.099999999999909</v>
       </c>
       <c r="U23" s="5"/>
@@ -3822,7 +3877,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="1"/>
+      <c r="AH23" s="1">
+        <f t="shared" si="12"/>
+        <v>32.327999999999996</v>
+      </c>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
@@ -3886,15 +3944,15 @@
         <v>89.801999999999992</v>
       </c>
       <c r="R24" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>146.76851999999974</v>
       </c>
       <c r="S24" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>146.76851999999974</v>
       </c>
       <c r="T24" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>146.76851999999974</v>
       </c>
       <c r="U24" s="5"/>
@@ -3936,7 +3994,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="1"/>
+      <c r="AH24" s="1">
+        <f t="shared" si="12"/>
+        <v>89.801999999999992</v>
+      </c>
       <c r="AI24" s="1"/>
       <c r="AJ24" s="1"/>
       <c r="AK24" s="1"/>
@@ -4002,15 +4063,15 @@
         <v>128.39339999999999</v>
       </c>
       <c r="R25" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>413.40067199999976</v>
       </c>
       <c r="S25" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>413.40067199999976</v>
       </c>
       <c r="T25" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>227.18415308108098</v>
       </c>
       <c r="U25" s="5">
@@ -4055,7 +4116,10 @@
         <f t="shared" si="11"/>
         <v>186</v>
       </c>
-      <c r="AH25" s="1"/>
+      <c r="AH25" s="1">
+        <f t="shared" si="12"/>
+        <v>128.39339999999999</v>
+      </c>
       <c r="AI25" s="1"/>
       <c r="AJ25" s="1"/>
       <c r="AK25" s="1"/>
@@ -4120,7 +4184,7 @@
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T26" s="5"/>
@@ -4165,7 +4229,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="1"/>
+      <c r="AH26" s="1">
+        <f t="shared" si="12"/>
+        <v>1.0192000000000001</v>
+      </c>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
@@ -4222,7 +4289,7 @@
       </c>
       <c r="R27" s="11"/>
       <c r="S27" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T27" s="11"/>
@@ -4265,7 +4332,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH27" s="1"/>
+      <c r="AH27" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
@@ -4331,15 +4401,15 @@
         <v>49.220399999999998</v>
       </c>
       <c r="R28" s="5">
-        <f t="shared" ref="R28:R81" si="21">12*Q28-P28-O28-F28</f>
+        <f t="shared" ref="R28:R81" si="22">12*Q28-P28-O28-F28</f>
         <v>329.86173800000006</v>
       </c>
       <c r="S28" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>329.86173800000006</v>
       </c>
       <c r="T28" s="5">
-        <f t="shared" ref="T28:T30" si="22">S28-U28</f>
+        <f t="shared" ref="T28:T30" si="23">S28-U28</f>
         <v>329.86173800000006</v>
       </c>
       <c r="U28" s="5"/>
@@ -4381,7 +4451,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="1"/>
+      <c r="AH28" s="1">
+        <f t="shared" si="12"/>
+        <v>49.220399999999998</v>
+      </c>
       <c r="AI28" s="1"/>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
@@ -4447,15 +4520,15 @@
         <v>37.422600000000003</v>
       </c>
       <c r="R29" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>168.97201200000012</v>
       </c>
       <c r="S29" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>168.97201200000012</v>
       </c>
       <c r="T29" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>168.97201200000012</v>
       </c>
       <c r="U29" s="5"/>
@@ -4497,7 +4570,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="1"/>
+      <c r="AH29" s="1">
+        <f t="shared" si="12"/>
+        <v>37.422600000000003</v>
+      </c>
       <c r="AI29" s="1"/>
       <c r="AJ29" s="1"/>
       <c r="AK29" s="1"/>
@@ -4563,7 +4639,7 @@
         <v>434.29799999999994</v>
       </c>
       <c r="R30" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>711.12637599999925</v>
       </c>
       <c r="S30" s="5">
@@ -4571,7 +4647,7 @@
         <v>994.72296999999924</v>
       </c>
       <c r="T30" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>546.64956009008972</v>
       </c>
       <c r="U30" s="5">
@@ -4616,7 +4692,10 @@
         <f t="shared" si="11"/>
         <v>448</v>
       </c>
-      <c r="AH30" s="1"/>
+      <c r="AH30" s="1">
+        <f t="shared" si="12"/>
+        <v>434.29799999999994</v>
+      </c>
       <c r="AI30" s="1"/>
       <c r="AJ30" s="1"/>
       <c r="AK30" s="1"/>
@@ -4681,7 +4760,7 @@
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T31" s="5"/>
@@ -4724,7 +4803,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="1"/>
+      <c r="AH31" s="1">
+        <f t="shared" si="12"/>
+        <v>3.278</v>
+      </c>
       <c r="AI31" s="1"/>
       <c r="AJ31" s="1"/>
       <c r="AK31" s="1"/>
@@ -4787,7 +4869,7 @@
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T32" s="5"/>
@@ -4830,7 +4912,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="1"/>
+      <c r="AH32" s="1">
+        <f t="shared" si="12"/>
+        <v>3.0420000000000003</v>
+      </c>
       <c r="AI32" s="1"/>
       <c r="AJ32" s="1"/>
       <c r="AK32" s="1"/>
@@ -4895,7 +4980,7 @@
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T33" s="5"/>
@@ -4938,7 +5023,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="1"/>
+      <c r="AH33" s="1">
+        <f t="shared" si="12"/>
+        <v>179.42860000000002</v>
+      </c>
       <c r="AI33" s="1"/>
       <c r="AJ33" s="1"/>
       <c r="AK33" s="1"/>
@@ -5004,15 +5092,15 @@
         <v>53.412800000000004</v>
       </c>
       <c r="R34" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>163.75946400000001</v>
       </c>
       <c r="S34" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>163.75946400000001</v>
       </c>
       <c r="T34" s="5">
-        <f t="shared" ref="T34:T37" si="23">S34-U34</f>
+        <f t="shared" ref="T34:T37" si="24">S34-U34</f>
         <v>163.75946400000001</v>
       </c>
       <c r="U34" s="5"/>
@@ -5054,7 +5142,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="1"/>
+      <c r="AH34" s="1">
+        <f t="shared" si="12"/>
+        <v>53.412800000000004</v>
+      </c>
       <c r="AI34" s="1"/>
       <c r="AJ34" s="1"/>
       <c r="AK34" s="1"/>
@@ -5120,7 +5211,7 @@
         <v>878.2</v>
       </c>
       <c r="R35" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1706.4160000000011</v>
       </c>
       <c r="S35" s="5">
@@ -5128,7 +5219,7 @@
         <v>2279.8806000000013</v>
       </c>
       <c r="T35" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1252.9073567567575</v>
       </c>
       <c r="U35" s="5">
@@ -5173,7 +5264,10 @@
         <f t="shared" si="11"/>
         <v>411</v>
       </c>
-      <c r="AH35" s="1"/>
+      <c r="AH35" s="1">
+        <f t="shared" si="12"/>
+        <v>351.28000000000003</v>
+      </c>
       <c r="AI35" s="1"/>
       <c r="AJ35" s="1"/>
       <c r="AK35" s="1"/>
@@ -5237,15 +5331,15 @@
         <v>83.2</v>
       </c>
       <c r="R36" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>258.63799999999998</v>
       </c>
       <c r="S36" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>258.63799999999998</v>
       </c>
       <c r="T36" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>258.63799999999998</v>
       </c>
       <c r="U36" s="5"/>
@@ -5287,7 +5381,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="1"/>
+      <c r="AH36" s="1">
+        <f t="shared" si="12"/>
+        <v>37.440000000000005</v>
+      </c>
       <c r="AI36" s="1"/>
       <c r="AJ36" s="1"/>
       <c r="AK36" s="1"/>
@@ -5353,7 +5450,7 @@
         <v>223.6</v>
       </c>
       <c r="R37" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1038.1400000000003</v>
       </c>
       <c r="S37" s="5">
@@ -5361,7 +5458,7 @@
         <v>1184.1508000000003</v>
       </c>
       <c r="T37" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>650.74953873873892</v>
       </c>
       <c r="U37" s="5">
@@ -5406,7 +5503,10 @@
         <f t="shared" si="11"/>
         <v>213</v>
       </c>
-      <c r="AH37" s="1"/>
+      <c r="AH37" s="1">
+        <f t="shared" si="12"/>
+        <v>89.44</v>
+      </c>
       <c r="AI37" s="1"/>
       <c r="AJ37" s="1"/>
       <c r="AK37" s="1"/>
@@ -5452,7 +5552,7 @@
         <v>28</v>
       </c>
       <c r="L38" s="1">
-        <f t="shared" ref="L38:L69" si="24">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="25">E38-K38</f>
         <v>-23</v>
       </c>
       <c r="M38" s="1"/>
@@ -5464,12 +5564,12 @@
         <v>12.866</v>
       </c>
       <c r="Q38" s="1">
-        <f t="shared" ref="Q38:Q69" si="25">E38/5</f>
+        <f t="shared" ref="Q38:Q69" si="26">E38/5</f>
         <v>1</v>
       </c>
       <c r="R38" s="5"/>
       <c r="S38" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T38" s="5"/>
@@ -5479,7 +5579,7 @@
         <v>42.635999999999996</v>
       </c>
       <c r="W38" s="1">
-        <f t="shared" ref="W38:W69" si="26">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="W38:W69" si="27">(F38+O38+P38)/Q38</f>
         <v>42.635999999999996</v>
       </c>
       <c r="X38" s="1">
@@ -5512,7 +5612,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="1"/>
+      <c r="AH38" s="1">
+        <f t="shared" si="12"/>
+        <v>0.4</v>
+      </c>
       <c r="AI38" s="1"/>
       <c r="AJ38" s="1"/>
       <c r="AK38" s="1"/>
@@ -5562,7 +5665,7 @@
         <v>301.89999999999998</v>
       </c>
       <c r="L39" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>16.007000000000005</v>
       </c>
       <c r="M39" s="1"/>
@@ -5574,15 +5677,15 @@
         <v>153.0941219999998</v>
       </c>
       <c r="Q39" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>63.581399999999995</v>
       </c>
       <c r="R39" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>437.55267800000013</v>
       </c>
       <c r="S39" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>437.55267800000013</v>
       </c>
       <c r="T39" s="5">
@@ -5598,7 +5701,7 @@
         <v>12</v>
       </c>
       <c r="W39" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.11822831834467</v>
       </c>
       <c r="X39" s="1">
@@ -5631,7 +5734,10 @@
         <f t="shared" si="11"/>
         <v>197</v>
       </c>
-      <c r="AH39" s="1"/>
+      <c r="AH39" s="1">
+        <f t="shared" si="12"/>
+        <v>63.581399999999995</v>
+      </c>
       <c r="AI39" s="1"/>
       <c r="AJ39" s="1"/>
       <c r="AK39" s="1"/>
@@ -5679,7 +5785,7 @@
         <v>243</v>
       </c>
       <c r="L40" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M40" s="1"/>
@@ -5689,12 +5795,12 @@
       </c>
       <c r="P40" s="1"/>
       <c r="Q40" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>48.6</v>
       </c>
       <c r="R40" s="5"/>
       <c r="S40" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T40" s="5"/>
@@ -5704,7 +5810,7 @@
         <v>41.563786008230451</v>
       </c>
       <c r="W40" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>41.563786008230451</v>
       </c>
       <c r="X40" s="1">
@@ -5739,7 +5845,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="1"/>
+      <c r="AH40" s="1">
+        <f t="shared" si="12"/>
+        <v>4.8600000000000003</v>
+      </c>
       <c r="AI40" s="1"/>
       <c r="AJ40" s="1"/>
       <c r="AK40" s="1"/>
@@ -5789,7 +5898,7 @@
         <v>308</v>
       </c>
       <c r="L41" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-23</v>
       </c>
       <c r="M41" s="1"/>
@@ -5801,19 +5910,19 @@
         <v>44.056000000000033</v>
       </c>
       <c r="Q41" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>57</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>474.94399999999996</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>474.94399999999996</v>
       </c>
       <c r="T41" s="5">
-        <f t="shared" ref="T41:T55" si="27">S41-U41</f>
+        <f t="shared" ref="T41:T55" si="28">S41-U41</f>
         <v>261.00526126126124</v>
       </c>
       <c r="U41" s="5">
@@ -5825,7 +5934,7 @@
         <v>12</v>
       </c>
       <c r="W41" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>3.6676491228070183</v>
       </c>
       <c r="X41" s="1">
@@ -5858,7 +5967,10 @@
         <f t="shared" si="11"/>
         <v>75</v>
       </c>
-      <c r="AH41" s="1"/>
+      <c r="AH41" s="1">
+        <f t="shared" si="12"/>
+        <v>19.95</v>
+      </c>
       <c r="AI41" s="1"/>
       <c r="AJ41" s="1"/>
       <c r="AK41" s="1"/>
@@ -5908,7 +6020,7 @@
         <v>48.25</v>
       </c>
       <c r="L42" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-9.1739999999999995</v>
       </c>
       <c r="M42" s="1"/>
@@ -5918,19 +6030,19 @@
       </c>
       <c r="P42" s="1"/>
       <c r="Q42" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>7.8151999999999999</v>
       </c>
       <c r="R42" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>36.779399999999995</v>
       </c>
       <c r="S42" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>36.779399999999995</v>
       </c>
       <c r="T42" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>36.779399999999995</v>
       </c>
       <c r="U42" s="5"/>
@@ -5939,7 +6051,7 @@
         <v>12</v>
       </c>
       <c r="W42" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>7.2938632408639572</v>
       </c>
       <c r="X42" s="1">
@@ -5972,7 +6084,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH42" s="1"/>
+      <c r="AH42" s="1">
+        <f t="shared" si="12"/>
+        <v>7.8151999999999999</v>
+      </c>
       <c r="AI42" s="1"/>
       <c r="AJ42" s="1"/>
       <c r="AK42" s="1"/>
@@ -6022,7 +6137,7 @@
         <v>243</v>
       </c>
       <c r="L43" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4</v>
       </c>
       <c r="M43" s="1"/>
@@ -6034,19 +6149,19 @@
         <v>158.23800000000011</v>
       </c>
       <c r="Q43" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>47.8</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>95.791999999999916</v>
       </c>
       <c r="S43" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>95.791999999999916</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>95.791999999999916</v>
       </c>
       <c r="U43" s="5"/>
@@ -6055,7 +6170,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="W43" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.9959832635983261</v>
       </c>
       <c r="X43" s="1">
@@ -6088,7 +6203,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="1"/>
+      <c r="AH43" s="1">
+        <f t="shared" si="12"/>
+        <v>19.12</v>
+      </c>
       <c r="AI43" s="1"/>
       <c r="AJ43" s="1"/>
       <c r="AK43" s="1"/>
@@ -6138,7 +6256,7 @@
         <v>204</v>
       </c>
       <c r="L44" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-3</v>
       </c>
       <c r="M44" s="1"/>
@@ -6150,19 +6268,19 @@
         <v>58.944000000000031</v>
       </c>
       <c r="Q44" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>40.200000000000003</v>
       </c>
       <c r="R44" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>78.596000000000004</v>
       </c>
       <c r="S44" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>78.596000000000004</v>
       </c>
       <c r="T44" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>78.596000000000004</v>
       </c>
       <c r="U44" s="5"/>
@@ -6171,7 +6289,7 @@
         <v>12</v>
       </c>
       <c r="W44" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.044875621890547</v>
       </c>
       <c r="X44" s="1">
@@ -6204,7 +6322,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH44" s="1"/>
+      <c r="AH44" s="1">
+        <f t="shared" si="12"/>
+        <v>16.080000000000002</v>
+      </c>
       <c r="AI44" s="1"/>
       <c r="AJ44" s="1"/>
       <c r="AK44" s="1"/>
@@ -6254,7 +6375,7 @@
         <v>144.07</v>
       </c>
       <c r="L45" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4.6659999999999968</v>
       </c>
       <c r="M45" s="1"/>
@@ -6266,19 +6387,19 @@
         <v>110.10204</v>
       </c>
       <c r="Q45" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>27.880800000000001</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>84.469182000000089</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>84.469182000000089</v>
       </c>
       <c r="T45" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>84.469182000000089</v>
       </c>
       <c r="U45" s="5"/>
@@ -6287,7 +6408,7 @@
         <v>12.000000000000004</v>
       </c>
       <c r="W45" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.9703458293879645</v>
       </c>
       <c r="X45" s="1">
@@ -6320,7 +6441,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="1"/>
+      <c r="AH45" s="1">
+        <f t="shared" si="12"/>
+        <v>27.880800000000001</v>
+      </c>
       <c r="AI45" s="1"/>
       <c r="AJ45" s="1"/>
       <c r="AK45" s="1"/>
@@ -6370,7 +6494,7 @@
         <v>1764</v>
       </c>
       <c r="L46" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-63</v>
       </c>
       <c r="M46" s="1"/>
@@ -6382,11 +6506,11 @@
         <v>941.19199999999989</v>
       </c>
       <c r="Q46" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>340.2</v>
       </c>
       <c r="R46" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2011.2079999999996</v>
       </c>
       <c r="S46" s="5">
@@ -6394,11 +6518,11 @@
         <v>2233.3585999999996</v>
       </c>
       <c r="T46" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1227.3412126126125</v>
       </c>
       <c r="U46" s="5">
-        <f t="shared" ref="U46:U48" si="28">S46/$U$1</f>
+        <f t="shared" ref="U46:U48" si="29">S46/$U$1</f>
         <v>1006.0173873873871</v>
       </c>
       <c r="V46" s="1">
@@ -6406,7 +6530,7 @@
         <v>12.652999999999999</v>
       </c>
       <c r="W46" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.0881599059376841</v>
       </c>
       <c r="X46" s="1">
@@ -6439,7 +6563,10 @@
         <f t="shared" si="11"/>
         <v>352</v>
       </c>
-      <c r="AH46" s="1"/>
+      <c r="AH46" s="1">
+        <f t="shared" si="12"/>
+        <v>119.07</v>
+      </c>
       <c r="AI46" s="1"/>
       <c r="AJ46" s="1"/>
       <c r="AK46" s="1"/>
@@ -6489,7 +6616,7 @@
         <v>642</v>
       </c>
       <c r="L47" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-14</v>
       </c>
       <c r="M47" s="1"/>
@@ -6501,23 +6628,23 @@
         <v>233.44399999999999</v>
       </c>
       <c r="Q47" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>125.6</v>
       </c>
       <c r="R47" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>419.26999999999964</v>
       </c>
       <c r="S47" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>419.26999999999964</v>
       </c>
       <c r="T47" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>230.40963963963947</v>
       </c>
       <c r="U47" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>188.86036036036018</v>
       </c>
       <c r="V47" s="1">
@@ -6525,7 +6652,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="W47" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.6618630573248439</v>
       </c>
       <c r="X47" s="1">
@@ -6558,7 +6685,10 @@
         <f t="shared" si="11"/>
         <v>76</v>
       </c>
-      <c r="AH47" s="1"/>
+      <c r="AH47" s="1">
+        <f t="shared" si="12"/>
+        <v>50.24</v>
+      </c>
       <c r="AI47" s="1"/>
       <c r="AJ47" s="1"/>
       <c r="AK47" s="1"/>
@@ -6608,7 +6738,7 @@
         <v>522.1</v>
       </c>
       <c r="L48" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>13.870999999999981</v>
       </c>
       <c r="M48" s="1"/>
@@ -6620,23 +6750,23 @@
         <v>346.52077999999977</v>
       </c>
       <c r="Q48" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>107.1942</v>
       </c>
       <c r="R48" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>592.17061999999999</v>
       </c>
       <c r="S48" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>592.17061999999999</v>
       </c>
       <c r="T48" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>325.4270974774775</v>
       </c>
       <c r="U48" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>266.74352252252248</v>
       </c>
       <c r="V48" s="1">
@@ -6644,7 +6774,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="W48" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.4757214476156335</v>
       </c>
       <c r="X48" s="1">
@@ -6677,7 +6807,10 @@
         <f t="shared" si="11"/>
         <v>267</v>
       </c>
-      <c r="AH48" s="1"/>
+      <c r="AH48" s="1">
+        <f t="shared" si="12"/>
+        <v>107.1942</v>
+      </c>
       <c r="AI48" s="1"/>
       <c r="AJ48" s="1"/>
       <c r="AK48" s="1"/>
@@ -6727,7 +6860,7 @@
         <v>528.9</v>
       </c>
       <c r="L49" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>14.220000000000027</v>
       </c>
       <c r="M49" s="1"/>
@@ -6739,19 +6872,19 @@
         <v>54.507253999999762</v>
       </c>
       <c r="Q49" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>108.624</v>
       </c>
       <c r="R49" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>277.27825800000016</v>
       </c>
       <c r="S49" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>277.27825800000016</v>
       </c>
       <c r="T49" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>277.27825800000016</v>
       </c>
       <c r="U49" s="5"/>
@@ -6760,7 +6893,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="W49" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.4473573243482072</v>
       </c>
       <c r="X49" s="1">
@@ -6793,7 +6926,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="1"/>
+      <c r="AH49" s="1">
+        <f t="shared" si="12"/>
+        <v>108.624</v>
+      </c>
       <c r="AI49" s="1"/>
       <c r="AJ49" s="1"/>
       <c r="AK49" s="1"/>
@@ -6843,7 +6979,7 @@
         <v>20</v>
       </c>
       <c r="L50" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-11.154</v>
       </c>
       <c r="M50" s="1"/>
@@ -6853,19 +6989,19 @@
       </c>
       <c r="P50" s="1"/>
       <c r="Q50" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.7692000000000001</v>
       </c>
       <c r="R50" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>3.6164000000000023</v>
       </c>
       <c r="S50" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.6164000000000023</v>
       </c>
       <c r="T50" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>3.6164000000000023</v>
       </c>
       <c r="U50" s="5"/>
@@ -6874,7 +7010,7 @@
         <v>12.000000000000002</v>
       </c>
       <c r="W50" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.9559122767352477</v>
       </c>
       <c r="X50" s="1">
@@ -6907,7 +7043,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="1"/>
+      <c r="AH50" s="1">
+        <f t="shared" si="12"/>
+        <v>1.7692000000000001</v>
+      </c>
       <c r="AI50" s="1"/>
       <c r="AJ50" s="1"/>
       <c r="AK50" s="1"/>
@@ -6957,7 +7096,7 @@
         <v>312</v>
       </c>
       <c r="L51" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-3</v>
       </c>
       <c r="M51" s="1"/>
@@ -6969,19 +7108,19 @@
         <v>25.293999999999858</v>
       </c>
       <c r="Q51" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>61.8</v>
       </c>
       <c r="R51" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>430.30600000000004</v>
       </c>
       <c r="S51" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>430.30600000000004</v>
       </c>
       <c r="T51" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>236.4744684684685</v>
       </c>
       <c r="U51" s="5">
@@ -6993,7 +7132,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="W51" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.0371197411003221</v>
       </c>
       <c r="X51" s="1">
@@ -7026,7 +7165,10 @@
         <f t="shared" si="11"/>
         <v>87</v>
       </c>
-      <c r="AH51" s="1"/>
+      <c r="AH51" s="1">
+        <f t="shared" si="12"/>
+        <v>27.81</v>
+      </c>
       <c r="AI51" s="1"/>
       <c r="AJ51" s="1"/>
       <c r="AK51" s="1"/>
@@ -7076,7 +7218,7 @@
         <v>466</v>
       </c>
       <c r="L52" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="M52" s="1"/>
@@ -7088,19 +7230,19 @@
         <v>93.480000000000132</v>
       </c>
       <c r="Q52" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>93</v>
       </c>
       <c r="R52" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>272</v>
       </c>
       <c r="S52" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>272</v>
       </c>
       <c r="T52" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>272</v>
       </c>
       <c r="U52" s="5"/>
@@ -7109,7 +7251,7 @@
         <v>12</v>
       </c>
       <c r="W52" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.0752688172043019</v>
       </c>
       <c r="X52" s="1">
@@ -7142,7 +7284,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH52" s="1"/>
+      <c r="AH52" s="1">
+        <f t="shared" si="12"/>
+        <v>41.85</v>
+      </c>
       <c r="AI52" s="1"/>
       <c r="AJ52" s="1"/>
       <c r="AK52" s="1"/>
@@ -7192,7 +7337,7 @@
         <v>184</v>
       </c>
       <c r="L53" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-27</v>
       </c>
       <c r="M53" s="1"/>
@@ -7204,19 +7349,19 @@
         <v>163.19200000000009</v>
       </c>
       <c r="Q53" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>31.4</v>
       </c>
       <c r="R53" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>150.12799999999987</v>
       </c>
       <c r="S53" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>150.12799999999987</v>
       </c>
       <c r="T53" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>150.12799999999987</v>
       </c>
       <c r="U53" s="5"/>
@@ -7225,7 +7370,7 @@
         <v>11.999999999999998</v>
       </c>
       <c r="W53" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>7.2188535031847163</v>
       </c>
       <c r="X53" s="1">
@@ -7258,7 +7403,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="1"/>
+      <c r="AH53" s="1">
+        <f t="shared" si="12"/>
+        <v>12.56</v>
+      </c>
       <c r="AI53" s="1"/>
       <c r="AJ53" s="1"/>
       <c r="AK53" s="1"/>
@@ -7306,7 +7454,7 @@
         <v>65</v>
       </c>
       <c r="L54" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-1</v>
       </c>
       <c r="M54" s="1"/>
@@ -7318,19 +7466,19 @@
         <v>39.200000000000003</v>
       </c>
       <c r="Q54" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>12.8</v>
       </c>
       <c r="R54" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>73.40000000000002</v>
       </c>
       <c r="S54" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>73.40000000000002</v>
       </c>
       <c r="T54" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>73.40000000000002</v>
       </c>
       <c r="U54" s="5"/>
@@ -7339,7 +7487,7 @@
         <v>12.000000000000002</v>
       </c>
       <c r="W54" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.265625</v>
       </c>
       <c r="X54" s="1">
@@ -7372,7 +7520,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="1"/>
+      <c r="AH54" s="1">
+        <f t="shared" si="12"/>
+        <v>5.120000000000001</v>
+      </c>
       <c r="AI54" s="1"/>
       <c r="AJ54" s="1"/>
       <c r="AK54" s="1"/>
@@ -7422,7 +7573,7 @@
         <v>755.5</v>
       </c>
       <c r="L55" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-3.4020000000000437</v>
       </c>
       <c r="M55" s="1"/>
@@ -7434,19 +7585,19 @@
         <v>284.03554999999989</v>
       </c>
       <c r="Q55" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>150.4196</v>
       </c>
       <c r="R55" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>475.76034000000027</v>
       </c>
       <c r="S55" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>475.76034000000027</v>
       </c>
       <c r="T55" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>261.45388054054069</v>
       </c>
       <c r="U55" s="5">
@@ -7458,7 +7609,7 @@
         <v>12</v>
       </c>
       <c r="W55" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.8371120518868533</v>
       </c>
       <c r="X55" s="1">
@@ -7491,7 +7642,10 @@
         <f t="shared" si="11"/>
         <v>214</v>
       </c>
-      <c r="AH55" s="1"/>
+      <c r="AH55" s="1">
+        <f t="shared" si="12"/>
+        <v>150.4196</v>
+      </c>
       <c r="AI55" s="1"/>
       <c r="AJ55" s="1"/>
       <c r="AK55" s="1"/>
@@ -7539,7 +7693,7 @@
         <v>145</v>
       </c>
       <c r="L56" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="M56" s="1"/>
@@ -7549,12 +7703,12 @@
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>29</v>
       </c>
       <c r="R56" s="5"/>
       <c r="S56" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T56" s="5"/>
@@ -7564,7 +7718,7 @@
         <v>38.137931034482762</v>
       </c>
       <c r="W56" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>38.137931034482762</v>
       </c>
       <c r="X56" s="1">
@@ -7599,7 +7753,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH56" s="1"/>
+      <c r="AH56" s="1">
+        <f t="shared" si="12"/>
+        <v>2.9000000000000004</v>
+      </c>
       <c r="AI56" s="1"/>
       <c r="AJ56" s="1"/>
       <c r="AK56" s="1"/>
@@ -7649,7 +7806,7 @@
         <v>668.3</v>
       </c>
       <c r="L57" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0.97100000000000364</v>
       </c>
       <c r="M57" s="1"/>
@@ -7659,19 +7816,19 @@
       </c>
       <c r="P57" s="1"/>
       <c r="Q57" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>133.85419999999999</v>
       </c>
       <c r="R57" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>400.45550199999957</v>
       </c>
       <c r="S57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>400.45550199999957</v>
       </c>
       <c r="T57" s="5">
-        <f t="shared" ref="T57:T58" si="29">S57-U57</f>
+        <f t="shared" ref="T57:T58" si="30">S57-U57</f>
         <v>220.07014073873853</v>
       </c>
       <c r="U57" s="5">
@@ -7683,7 +7840,7 @@
         <v>12</v>
       </c>
       <c r="W57" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.0082709246329244</v>
       </c>
       <c r="X57" s="1">
@@ -7716,7 +7873,10 @@
         <f t="shared" si="11"/>
         <v>180</v>
       </c>
-      <c r="AH57" s="1"/>
+      <c r="AH57" s="1">
+        <f t="shared" si="12"/>
+        <v>133.85419999999999</v>
+      </c>
       <c r="AI57" s="1"/>
       <c r="AJ57" s="1"/>
       <c r="AK57" s="1"/>
@@ -7764,7 +7924,7 @@
         <v>100.15</v>
       </c>
       <c r="L58" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3.1430000000000007</v>
       </c>
       <c r="M58" s="1"/>
@@ -7776,19 +7936,19 @@
         <v>13.54782599999999</v>
       </c>
       <c r="Q58" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>20.6586</v>
       </c>
       <c r="R58" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>51.003244000000024</v>
       </c>
       <c r="S58" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>51.003244000000024</v>
       </c>
       <c r="T58" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>51.003244000000024</v>
       </c>
       <c r="U58" s="5"/>
@@ -7797,7 +7957,7 @@
         <v>12</v>
       </c>
       <c r="W58" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.5311374439700653</v>
       </c>
       <c r="X58" s="1">
@@ -7830,7 +7990,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH58" s="1"/>
+      <c r="AH58" s="1">
+        <f t="shared" si="12"/>
+        <v>20.6586</v>
+      </c>
       <c r="AI58" s="1"/>
       <c r="AJ58" s="1"/>
       <c r="AK58" s="1"/>
@@ -7878,7 +8041,7 @@
         <v>145</v>
       </c>
       <c r="L59" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2</v>
       </c>
       <c r="M59" s="1"/>
@@ -7888,12 +8051,12 @@
       </c>
       <c r="P59" s="1"/>
       <c r="Q59" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>28.6</v>
       </c>
       <c r="R59" s="5"/>
       <c r="S59" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T59" s="5"/>
@@ -7903,7 +8066,7 @@
         <v>25.384615384615383</v>
       </c>
       <c r="W59" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>25.384615384615383</v>
       </c>
       <c r="X59" s="1">
@@ -7938,7 +8101,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH59" s="1"/>
+      <c r="AH59" s="1">
+        <f t="shared" si="12"/>
+        <v>2.8600000000000003</v>
+      </c>
       <c r="AI59" s="1"/>
       <c r="AJ59" s="1"/>
       <c r="AK59" s="1"/>
@@ -7988,7 +8154,7 @@
         <v>224</v>
       </c>
       <c r="L60" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-4</v>
       </c>
       <c r="M60" s="1"/>
@@ -7998,15 +8164,15 @@
       </c>
       <c r="P60" s="1"/>
       <c r="Q60" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>44</v>
       </c>
       <c r="R60" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>72.742000000000075</v>
       </c>
       <c r="S60" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>72.742000000000075</v>
       </c>
       <c r="T60" s="5">
@@ -8019,7 +8185,7 @@
         <v>12</v>
       </c>
       <c r="W60" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10.346772727272725</v>
       </c>
       <c r="X60" s="1">
@@ -8052,7 +8218,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH60" s="1"/>
+      <c r="AH60" s="1">
+        <f t="shared" si="12"/>
+        <v>17.600000000000001</v>
+      </c>
       <c r="AI60" s="1"/>
       <c r="AJ60" s="1"/>
       <c r="AK60" s="1"/>
@@ -8102,7 +8271,7 @@
         <v>23.6</v>
       </c>
       <c r="L61" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2.0470000000000006</v>
       </c>
       <c r="M61" s="1"/>
@@ -8112,12 +8281,12 @@
       </c>
       <c r="P61" s="1"/>
       <c r="Q61" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>4.3106</v>
       </c>
       <c r="R61" s="5"/>
       <c r="S61" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T61" s="5"/>
@@ -8127,7 +8296,7 @@
         <v>16.841640142903536</v>
       </c>
       <c r="W61" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>16.841640142903536</v>
       </c>
       <c r="X61" s="1">
@@ -8160,7 +8329,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="1"/>
+      <c r="AH61" s="1">
+        <f t="shared" si="12"/>
+        <v>4.3106</v>
+      </c>
       <c r="AI61" s="1"/>
       <c r="AJ61" s="1"/>
       <c r="AK61" s="1"/>
@@ -8206,7 +8378,7 @@
         <v>21</v>
       </c>
       <c r="L62" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-21</v>
       </c>
       <c r="M62" s="1"/>
@@ -8216,12 +8388,12 @@
       </c>
       <c r="P62" s="1"/>
       <c r="Q62" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="R62" s="5"/>
       <c r="S62" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T62" s="5"/>
@@ -8231,7 +8403,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="W62" s="1" t="e">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X62" s="1">
@@ -8266,7 +8438,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH62" s="1"/>
+      <c r="AH62" s="1">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
       <c r="AI62" s="1"/>
       <c r="AJ62" s="1"/>
       <c r="AK62" s="1"/>
@@ -8316,7 +8491,7 @@
         <v>851</v>
       </c>
       <c r="L63" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-21</v>
       </c>
       <c r="M63" s="1"/>
@@ -8328,19 +8503,19 @@
         <v>533.71600000000001</v>
       </c>
       <c r="Q63" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>166</v>
       </c>
       <c r="R63" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>895.28400000000011</v>
       </c>
       <c r="S63" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>895.28400000000011</v>
       </c>
       <c r="T63" s="5">
-        <f t="shared" ref="T63:T68" si="30">S63-U63</f>
+        <f t="shared" ref="T63:T68" si="31">S63-U63</f>
         <v>492.00291891891902</v>
       </c>
       <c r="U63" s="5">
@@ -8352,7 +8527,7 @@
         <v>12</v>
       </c>
       <c r="W63" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.6067228915662648</v>
       </c>
       <c r="X63" s="1">
@@ -8385,7 +8560,10 @@
         <f t="shared" si="11"/>
         <v>161</v>
       </c>
-      <c r="AH63" s="1"/>
+      <c r="AH63" s="1">
+        <f t="shared" si="12"/>
+        <v>66.400000000000006</v>
+      </c>
       <c r="AI63" s="1"/>
       <c r="AJ63" s="1"/>
       <c r="AK63" s="1"/>
@@ -8435,7 +8613,7 @@
         <v>584</v>
       </c>
       <c r="L64" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-24</v>
       </c>
       <c r="M64" s="1"/>
@@ -8447,19 +8625,19 @@
         <v>123.536</v>
       </c>
       <c r="Q64" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>112</v>
       </c>
       <c r="R64" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>369.61199999999997</v>
       </c>
       <c r="S64" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>369.61199999999997</v>
       </c>
       <c r="T64" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>369.61199999999997</v>
       </c>
       <c r="U64" s="5"/>
@@ -8468,7 +8646,7 @@
         <v>12</v>
       </c>
       <c r="W64" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.6998928571428564</v>
       </c>
       <c r="X64" s="1">
@@ -8501,7 +8679,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH64" s="1"/>
+      <c r="AH64" s="1">
+        <f t="shared" si="12"/>
+        <v>44.800000000000004</v>
+      </c>
       <c r="AI64" s="1"/>
       <c r="AJ64" s="1"/>
       <c r="AK64" s="1"/>
@@ -8551,7 +8732,7 @@
         <v>282.35000000000002</v>
       </c>
       <c r="L65" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-0.53800000000001091</v>
       </c>
       <c r="M65" s="1"/>
@@ -8563,19 +8744,19 @@
         <v>175.0586679999999</v>
       </c>
       <c r="Q65" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>56.362400000000001</v>
       </c>
       <c r="R65" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>149.56893399999987</v>
       </c>
       <c r="S65" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>149.56893399999987</v>
       </c>
       <c r="T65" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>149.56893399999987</v>
       </c>
       <c r="U65" s="5"/>
@@ -8584,7 +8765,7 @@
         <v>12</v>
       </c>
       <c r="W65" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.3462994123742078</v>
       </c>
       <c r="X65" s="1">
@@ -8617,7 +8798,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH65" s="1"/>
+      <c r="AH65" s="1">
+        <f t="shared" si="12"/>
+        <v>56.362400000000001</v>
+      </c>
       <c r="AI65" s="1"/>
       <c r="AJ65" s="1"/>
       <c r="AK65" s="1"/>
@@ -8667,7 +8851,7 @@
         <v>236.3</v>
       </c>
       <c r="L66" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.0889999999999986</v>
       </c>
       <c r="M66" s="1"/>
@@ -8677,19 +8861,19 @@
       </c>
       <c r="P66" s="1"/>
       <c r="Q66" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>48.477800000000002</v>
       </c>
       <c r="R66" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>260.04260000000005</v>
       </c>
       <c r="S66" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>260.04260000000005</v>
       </c>
       <c r="T66" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>260.04260000000005</v>
       </c>
       <c r="U66" s="5"/>
@@ -8698,7 +8882,7 @@
         <v>12</v>
       </c>
       <c r="W66" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6.6358415604668517</v>
       </c>
       <c r="X66" s="1">
@@ -8731,7 +8915,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH66" s="1"/>
+      <c r="AH66" s="1">
+        <f t="shared" si="12"/>
+        <v>48.477800000000002</v>
+      </c>
       <c r="AI66" s="1"/>
       <c r="AJ66" s="1"/>
       <c r="AK66" s="1"/>
@@ -8781,7 +8968,7 @@
         <v>921.9</v>
       </c>
       <c r="L67" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>28.199000000000069</v>
       </c>
       <c r="M67" s="1"/>
@@ -8793,19 +8980,19 @@
         <v>901.43566400000032</v>
       </c>
       <c r="Q67" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>190.0198</v>
       </c>
       <c r="R67" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>432.04021599999999</v>
       </c>
       <c r="S67" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>432.04021599999999</v>
       </c>
       <c r="T67" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>237.42750609009011</v>
       </c>
       <c r="U67" s="5">
@@ -8817,7 +9004,7 @@
         <v>12</v>
       </c>
       <c r="W67" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>9.7263410655100149</v>
       </c>
       <c r="X67" s="1">
@@ -8850,7 +9037,10 @@
         <f t="shared" si="11"/>
         <v>195</v>
       </c>
-      <c r="AH67" s="1"/>
+      <c r="AH67" s="1">
+        <f t="shared" si="12"/>
+        <v>190.0198</v>
+      </c>
       <c r="AI67" s="1"/>
       <c r="AJ67" s="1"/>
       <c r="AK67" s="1"/>
@@ -8900,7 +9090,7 @@
         <v>257.5</v>
       </c>
       <c r="L68" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-8.9770000000000039</v>
       </c>
       <c r="M68" s="1"/>
@@ -8912,19 +9102,19 @@
         <v>193.90915400000009</v>
       </c>
       <c r="Q68" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>49.704599999999999</v>
       </c>
       <c r="R68" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>163.98933200000005</v>
       </c>
       <c r="S68" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>163.98933200000005</v>
       </c>
       <c r="T68" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>163.98933200000005</v>
       </c>
       <c r="U68" s="5"/>
@@ -8933,7 +9123,7 @@
         <v>12.000000000000002</v>
       </c>
       <c r="W68" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8.7007212209735112</v>
       </c>
       <c r="X68" s="1">
@@ -8966,7 +9156,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH68" s="1"/>
+      <c r="AH68" s="1">
+        <f t="shared" si="12"/>
+        <v>49.704599999999999</v>
+      </c>
       <c r="AI68" s="1"/>
       <c r="AJ68" s="1"/>
       <c r="AK68" s="1"/>
@@ -9016,7 +9209,7 @@
         <v>11</v>
       </c>
       <c r="L69" s="1">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-2</v>
       </c>
       <c r="M69" s="1"/>
@@ -9028,12 +9221,12 @@
         <v>6.0140000000000011</v>
       </c>
       <c r="Q69" s="1">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>1.8</v>
       </c>
       <c r="R69" s="5"/>
       <c r="S69" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T69" s="5"/>
@@ -9043,7 +9236,7 @@
         <v>13.285555555555556</v>
       </c>
       <c r="W69" s="1">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13.285555555555556</v>
       </c>
       <c r="X69" s="1">
@@ -9076,7 +9269,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH69" s="1"/>
+      <c r="AH69" s="1">
+        <f t="shared" si="12"/>
+        <v>1.08</v>
+      </c>
       <c r="AI69" s="1"/>
       <c r="AJ69" s="1"/>
       <c r="AK69" s="1"/>
@@ -9126,7 +9322,7 @@
         <v>407.75</v>
       </c>
       <c r="L70" s="1">
-        <f t="shared" ref="L70:L101" si="31">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="32">E70-K70</f>
         <v>-29.514999999999986</v>
       </c>
       <c r="M70" s="1"/>
@@ -9136,12 +9332,12 @@
       </c>
       <c r="P70" s="1"/>
       <c r="Q70" s="1">
-        <f t="shared" ref="Q70:Q101" si="32">E70/5</f>
+        <f t="shared" ref="Q70:Q101" si="33">E70/5</f>
         <v>75.647000000000006</v>
       </c>
       <c r="R70" s="5"/>
       <c r="S70" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="T70" s="5"/>
@@ -9151,7 +9347,7 @@
         <v>15.466548574299047</v>
       </c>
       <c r="W70" s="1">
-        <f t="shared" ref="W70:W101" si="33">(F70+O70+P70)/Q70</f>
+        <f t="shared" ref="W70:W101" si="34">(F70+O70+P70)/Q70</f>
         <v>15.466548574299047</v>
       </c>
       <c r="X70" s="1">
@@ -9184,7 +9380,10 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH70" s="1"/>
+      <c r="AH70" s="1">
+        <f t="shared" si="12"/>
+        <v>75.647000000000006</v>
+      </c>
       <c r="AI70" s="1"/>
       <c r="AJ70" s="1"/>
       <c r="AK70" s="1"/>
@@ -9234,7 +9433,7 @@
         <v>101</v>
       </c>
       <c r="L71" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="M71" s="1"/>
@@ -9244,15 +9443,15 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>20</v>
       </c>
       <c r="R71" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>80.074000000000098</v>
       </c>
       <c r="S71" s="5">
-        <f t="shared" ref="S71:S124" si="34">R71</f>
+        <f t="shared" ref="S71:S124" si="35">R71</f>
         <v>80.074000000000098</v>
       </c>
       <c r="T71" s="5">
@@ -9261,11 +9460,11 @@
       </c>
       <c r="U71" s="5"/>
       <c r="V71" s="1">
-        <f t="shared" ref="V71:V124" si="35">(F71+O71+P71+S71)/Q71</f>
+        <f t="shared" ref="V71:V124" si="36">(F71+O71+P71+S71)/Q71</f>
         <v>12</v>
       </c>
       <c r="W71" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>7.9962999999999953</v>
       </c>
       <c r="X71" s="1">
@@ -9291,14 +9490,17 @@
       </c>
       <c r="AE71" s="1"/>
       <c r="AF71" s="1">
-        <f t="shared" ref="AF71:AF124" si="36">ROUND(G71*T71,0)</f>
+        <f t="shared" ref="AF71:AF124" si="37">ROUND(G71*T71,0)</f>
         <v>48</v>
       </c>
       <c r="AG71" s="1">
-        <f t="shared" ref="AG71:AG124" si="37">ROUND(G71*U71,0)</f>
+        <f t="shared" ref="AG71:AG124" si="38">ROUND(G71*U71,0)</f>
         <v>0</v>
       </c>
-      <c r="AH71" s="1"/>
+      <c r="AH71" s="1">
+        <f t="shared" ref="AH71:AH124" si="39">Q71*G71</f>
+        <v>12</v>
+      </c>
       <c r="AI71" s="1"/>
       <c r="AJ71" s="1"/>
       <c r="AK71" s="1"/>
@@ -9346,7 +9548,7 @@
         <v>28</v>
       </c>
       <c r="L72" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M72" s="1"/>
@@ -9358,22 +9560,22 @@
         <v>7.4960000000000004</v>
       </c>
       <c r="Q72" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>5.6</v>
       </c>
       <c r="R72" s="5"/>
       <c r="S72" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T72" s="5"/>
       <c r="U72" s="5"/>
       <c r="V72" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.83678571428571</v>
       </c>
       <c r="W72" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.83678571428571</v>
       </c>
       <c r="X72" s="1">
@@ -9399,14 +9601,17 @@
       </c>
       <c r="AE72" s="1"/>
       <c r="AF72" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG72" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH72" s="1"/>
+      <c r="AG72" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH72" s="1">
+        <f t="shared" si="39"/>
+        <v>3.36</v>
+      </c>
       <c r="AI72" s="1"/>
       <c r="AJ72" s="1"/>
       <c r="AK72" s="1"/>
@@ -9456,7 +9661,7 @@
         <v>94</v>
       </c>
       <c r="L73" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M73" s="1"/>
@@ -9466,28 +9671,28 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>18.8</v>
       </c>
       <c r="R73" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>101.60000000000002</v>
       </c>
       <c r="S73" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>101.60000000000002</v>
       </c>
       <c r="T73" s="5">
-        <f t="shared" ref="T73:T76" si="38">S73-U73</f>
+        <f t="shared" ref="T73:T76" si="40">S73-U73</f>
         <v>101.60000000000002</v>
       </c>
       <c r="U73" s="5"/>
       <c r="V73" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W73" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.5957446808510634</v>
       </c>
       <c r="X73" s="1">
@@ -9513,14 +9718,17 @@
       </c>
       <c r="AE73" s="1"/>
       <c r="AF73" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>41</v>
       </c>
       <c r="AG73" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH73" s="1"/>
+      <c r="AH73" s="1">
+        <f t="shared" si="39"/>
+        <v>7.5200000000000005</v>
+      </c>
       <c r="AI73" s="1"/>
       <c r="AJ73" s="1"/>
       <c r="AK73" s="1"/>
@@ -9570,7 +9778,7 @@
         <v>108</v>
       </c>
       <c r="L74" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="M74" s="1"/>
@@ -9580,28 +9788,28 @@
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>21.4</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>102.79999999999995</v>
       </c>
       <c r="S74" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>102.79999999999995</v>
       </c>
       <c r="T74" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>102.79999999999995</v>
       </c>
       <c r="U74" s="5"/>
       <c r="V74" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W74" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>7.1962616822429908</v>
       </c>
       <c r="X74" s="1">
@@ -9627,14 +9835,17 @@
       </c>
       <c r="AE74" s="1"/>
       <c r="AF74" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>34</v>
       </c>
       <c r="AG74" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH74" s="1"/>
+      <c r="AH74" s="1">
+        <f t="shared" si="39"/>
+        <v>7.0620000000000003</v>
+      </c>
       <c r="AI74" s="1"/>
       <c r="AJ74" s="1"/>
       <c r="AK74" s="1"/>
@@ -9684,7 +9895,7 @@
         <v>91</v>
       </c>
       <c r="L75" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-6</v>
       </c>
       <c r="M75" s="1"/>
@@ -9694,28 +9905,28 @@
       </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>17</v>
       </c>
       <c r="R75" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>144</v>
       </c>
       <c r="S75" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>144</v>
       </c>
       <c r="T75" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>144</v>
       </c>
       <c r="U75" s="5"/>
       <c r="V75" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W75" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>3.5294117647058822</v>
       </c>
       <c r="X75" s="1">
@@ -9741,14 +9952,17 @@
       </c>
       <c r="AE75" s="1"/>
       <c r="AF75" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>50</v>
       </c>
       <c r="AG75" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH75" s="1"/>
+      <c r="AH75" s="1">
+        <f t="shared" si="39"/>
+        <v>5.9499999999999993</v>
+      </c>
       <c r="AI75" s="1"/>
       <c r="AJ75" s="1"/>
       <c r="AK75" s="1"/>
@@ -9798,7 +10012,7 @@
         <v>548</v>
       </c>
       <c r="L76" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-14</v>
       </c>
       <c r="M76" s="1"/>
@@ -9810,28 +10024,28 @@
         <v>105.096</v>
       </c>
       <c r="Q76" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>106.8</v>
       </c>
       <c r="R76" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>284.10399999999993</v>
       </c>
       <c r="S76" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>284.10399999999993</v>
       </c>
       <c r="T76" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>284.10399999999993</v>
       </c>
       <c r="U76" s="5"/>
       <c r="V76" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W76" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.3398501872659185</v>
       </c>
       <c r="X76" s="1">
@@ -9857,14 +10071,17 @@
       </c>
       <c r="AE76" s="1"/>
       <c r="AF76" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>105</v>
       </c>
       <c r="AG76" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH76" s="1"/>
+      <c r="AH76" s="1">
+        <f t="shared" si="39"/>
+        <v>39.515999999999998</v>
+      </c>
       <c r="AI76" s="1"/>
       <c r="AJ76" s="1"/>
       <c r="AK76" s="1"/>
@@ -9914,7 +10131,7 @@
         <v>90</v>
       </c>
       <c r="L77" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-2</v>
       </c>
       <c r="M77" s="1"/>
@@ -9924,22 +10141,22 @@
       </c>
       <c r="P77" s="1"/>
       <c r="Q77" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>17.600000000000001</v>
       </c>
       <c r="R77" s="5"/>
       <c r="S77" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T77" s="5"/>
       <c r="U77" s="5"/>
       <c r="V77" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17.515909090909087</v>
       </c>
       <c r="W77" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>17.515909090909087</v>
       </c>
       <c r="X77" s="1">
@@ -9965,14 +10182,17 @@
       </c>
       <c r="AE77" s="1"/>
       <c r="AF77" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG77" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH77" s="1"/>
+      <c r="AG77" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH77" s="1">
+        <f t="shared" si="39"/>
+        <v>10.56</v>
+      </c>
       <c r="AI77" s="1"/>
       <c r="AJ77" s="1"/>
       <c r="AK77" s="1"/>
@@ -10022,7 +10242,7 @@
         <v>36</v>
       </c>
       <c r="L78" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-17</v>
       </c>
       <c r="M78" s="1"/>
@@ -10032,22 +10252,22 @@
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3.8</v>
       </c>
       <c r="R78" s="5"/>
       <c r="S78" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T78" s="5"/>
       <c r="U78" s="5"/>
       <c r="V78" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>17.368421052631579</v>
       </c>
       <c r="W78" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>17.368421052631579</v>
       </c>
       <c r="X78" s="1">
@@ -10073,14 +10293,17 @@
       </c>
       <c r="AE78" s="1"/>
       <c r="AF78" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG78" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH78" s="1"/>
+      <c r="AG78" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH78" s="1">
+        <f t="shared" si="39"/>
+        <v>1.254</v>
+      </c>
       <c r="AI78" s="1"/>
       <c r="AJ78" s="1"/>
       <c r="AK78" s="1"/>
@@ -10130,7 +10353,7 @@
         <v>275</v>
       </c>
       <c r="L79" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-4</v>
       </c>
       <c r="M79" s="1"/>
@@ -10142,28 +10365,28 @@
         <v>43.117999999999981</v>
       </c>
       <c r="Q79" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>54.2</v>
       </c>
       <c r="R79" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>187.07400000000007</v>
       </c>
       <c r="S79" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>187.07400000000007</v>
       </c>
       <c r="T79" s="5">
-        <f t="shared" ref="T79:T81" si="39">S79-U79</f>
+        <f t="shared" ref="T79:T81" si="41">S79-U79</f>
         <v>187.07400000000007</v>
       </c>
       <c r="U79" s="5"/>
       <c r="V79" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W79" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>8.5484501845018457</v>
       </c>
       <c r="X79" s="1">
@@ -10189,14 +10412,17 @@
       </c>
       <c r="AE79" s="1"/>
       <c r="AF79" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>75</v>
       </c>
       <c r="AG79" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH79" s="1"/>
+      <c r="AH79" s="1">
+        <f t="shared" si="39"/>
+        <v>21.680000000000003</v>
+      </c>
       <c r="AI79" s="1"/>
       <c r="AJ79" s="1"/>
       <c r="AK79" s="1"/>
@@ -10246,7 +10472,7 @@
         <v>115</v>
       </c>
       <c r="L80" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-12</v>
       </c>
       <c r="M80" s="1"/>
@@ -10256,28 +10482,28 @@
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>20.6</v>
       </c>
       <c r="R80" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>106.20000000000002</v>
       </c>
       <c r="S80" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>106.20000000000002</v>
       </c>
       <c r="T80" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>106.20000000000002</v>
       </c>
       <c r="U80" s="5"/>
       <c r="V80" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W80" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.8446601941747565</v>
       </c>
       <c r="X80" s="1">
@@ -10303,14 +10529,17 @@
       </c>
       <c r="AE80" s="1"/>
       <c r="AF80" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>37</v>
       </c>
       <c r="AG80" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH80" s="1"/>
+      <c r="AH80" s="1">
+        <f t="shared" si="39"/>
+        <v>7.21</v>
+      </c>
       <c r="AI80" s="1"/>
       <c r="AJ80" s="1"/>
       <c r="AK80" s="1"/>
@@ -10360,7 +10589,7 @@
         <v>165</v>
       </c>
       <c r="L81" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-4</v>
       </c>
       <c r="M81" s="1"/>
@@ -10370,28 +10599,28 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>32.200000000000003</v>
       </c>
       <c r="R81" s="5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>68.400000000000034</v>
       </c>
       <c r="S81" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>68.400000000000034</v>
       </c>
       <c r="T81" s="5">
-        <f t="shared" si="39"/>
+        <f t="shared" si="41"/>
         <v>68.400000000000034</v>
       </c>
       <c r="U81" s="5"/>
       <c r="V81" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W81" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.8757763975155264</v>
       </c>
       <c r="X81" s="1">
@@ -10417,14 +10646,17 @@
       </c>
       <c r="AE81" s="1"/>
       <c r="AF81" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>24</v>
       </c>
       <c r="AG81" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH81" s="1"/>
+      <c r="AH81" s="1">
+        <f t="shared" si="39"/>
+        <v>11.27</v>
+      </c>
       <c r="AI81" s="1"/>
       <c r="AJ81" s="1"/>
       <c r="AK81" s="1"/>
@@ -10474,7 +10706,7 @@
         <v>6</v>
       </c>
       <c r="L82" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="M82" s="1"/>
@@ -10484,22 +10716,22 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>1</v>
       </c>
       <c r="R82" s="5"/>
       <c r="S82" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T82" s="5"/>
       <c r="U82" s="5"/>
       <c r="V82" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>212</v>
       </c>
       <c r="W82" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>212</v>
       </c>
       <c r="X82" s="1">
@@ -10527,14 +10759,17 @@
         <v>105</v>
       </c>
       <c r="AF82" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG82" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH82" s="1"/>
+      <c r="AG82" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH82" s="1">
+        <f t="shared" si="39"/>
+        <v>0.4</v>
+      </c>
       <c r="AI82" s="1"/>
       <c r="AJ82" s="1"/>
       <c r="AK82" s="1"/>
@@ -10580,7 +10815,7 @@
         <v>22</v>
       </c>
       <c r="L83" s="9">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1.0859999999999985</v>
       </c>
       <c r="M83" s="9"/>
@@ -10590,22 +10825,22 @@
       </c>
       <c r="P83" s="9"/>
       <c r="Q83" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.6171999999999995</v>
       </c>
       <c r="R83" s="11"/>
       <c r="S83" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T83" s="11"/>
       <c r="U83" s="11"/>
       <c r="V83" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>27.606124924196486</v>
       </c>
       <c r="W83" s="9">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>27.606124924196486</v>
       </c>
       <c r="X83" s="9">
@@ -10633,14 +10868,17 @@
         <v>105</v>
       </c>
       <c r="AF83" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG83" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH83" s="1"/>
+      <c r="AG83" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH83" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AI83" s="1"/>
       <c r="AJ83" s="1"/>
       <c r="AK83" s="1"/>
@@ -10688,7 +10926,7 @@
         <v>17</v>
       </c>
       <c r="L84" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M84" s="1"/>
@@ -10698,28 +10936,28 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3.4</v>
       </c>
       <c r="R84" s="5">
-        <f t="shared" ref="R84:R122" si="40">12*Q84-P84-O84-F84</f>
+        <f t="shared" ref="R84:R122" si="42">12*Q84-P84-O84-F84</f>
         <v>17.799999999999997</v>
       </c>
       <c r="S84" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.799999999999997</v>
       </c>
       <c r="T84" s="5">
-        <f t="shared" ref="T84:T89" si="41">S84-U84</f>
+        <f t="shared" ref="T84:T89" si="43">S84-U84</f>
         <v>17.799999999999997</v>
       </c>
       <c r="U84" s="5"/>
       <c r="V84" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W84" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>6.7647058823529411</v>
       </c>
       <c r="X84" s="1">
@@ -10745,14 +10983,17 @@
       </c>
       <c r="AE84" s="1"/>
       <c r="AF84" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>7</v>
       </c>
       <c r="AG84" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH84" s="1"/>
+      <c r="AH84" s="1">
+        <f t="shared" si="39"/>
+        <v>1.36</v>
+      </c>
       <c r="AI84" s="1"/>
       <c r="AJ84" s="1"/>
       <c r="AK84" s="1"/>
@@ -10800,7 +11041,7 @@
         <v>201.7</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>17.491000000000014</v>
       </c>
       <c r="M85" s="1"/>
@@ -10810,28 +11051,28 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>43.838200000000001</v>
       </c>
       <c r="R85" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>144.02678999999998</v>
       </c>
       <c r="S85" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>144.02678999999998</v>
       </c>
       <c r="T85" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>144.02678999999998</v>
       </c>
       <c r="U85" s="5"/>
       <c r="V85" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W85" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>8.7145824874196478</v>
       </c>
       <c r="X85" s="1">
@@ -10857,14 +11098,17 @@
       </c>
       <c r="AE85" s="1"/>
       <c r="AF85" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>144</v>
       </c>
       <c r="AG85" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH85" s="1"/>
+      <c r="AH85" s="1">
+        <f t="shared" si="39"/>
+        <v>43.838200000000001</v>
+      </c>
       <c r="AI85" s="1"/>
       <c r="AJ85" s="1"/>
       <c r="AK85" s="1"/>
@@ -10914,7 +11158,7 @@
         <v>1031.4649999999999</v>
       </c>
       <c r="L86" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-3.862999999999829</v>
       </c>
       <c r="M86" s="1"/>
@@ -10926,31 +11170,31 @@
         <v>708.45563800000025</v>
       </c>
       <c r="Q86" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>205.52040000000002</v>
       </c>
       <c r="R86" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>350.39943200000016</v>
       </c>
       <c r="S86" s="5">
-        <f t="shared" ref="S86:S89" si="42">R86+Q86*$S$1</f>
+        <f t="shared" ref="S86:S89" si="44">R86+Q86*$S$1</f>
         <v>484.60425320000019</v>
       </c>
       <c r="T86" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>266.314049055856</v>
       </c>
       <c r="U86" s="5">
-        <f t="shared" ref="U86:U89" si="43">S86/$U$1</f>
+        <f t="shared" ref="U86:U89" si="45">S86/$U$1</f>
         <v>218.29020414414421</v>
       </c>
       <c r="V86" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.653</v>
       </c>
       <c r="W86" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.295062524206843</v>
       </c>
       <c r="X86" s="1">
@@ -10976,14 +11220,17 @@
       </c>
       <c r="AE86" s="1"/>
       <c r="AF86" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>266</v>
       </c>
       <c r="AG86" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>218</v>
       </c>
-      <c r="AH86" s="1"/>
+      <c r="AH86" s="1">
+        <f t="shared" si="39"/>
+        <v>205.52040000000002</v>
+      </c>
       <c r="AI86" s="1"/>
       <c r="AJ86" s="1"/>
       <c r="AK86" s="1"/>
@@ -11033,7 +11280,7 @@
         <v>2056.9</v>
       </c>
       <c r="L87" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>25.365999999999985</v>
       </c>
       <c r="M87" s="1"/>
@@ -11045,31 +11292,31 @@
         <v>210.4736719999996</v>
       </c>
       <c r="Q87" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>416.45320000000004</v>
       </c>
       <c r="R87" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>905.12372800000185</v>
       </c>
       <c r="S87" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1177.0676676000019</v>
       </c>
       <c r="T87" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>646.85700651892</v>
       </c>
       <c r="U87" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>530.21066108108187</v>
       </c>
       <c r="V87" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.653000000000002</v>
       </c>
       <c r="W87" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.8265895711690998</v>
       </c>
       <c r="X87" s="1">
@@ -11095,14 +11342,17 @@
       </c>
       <c r="AE87" s="1"/>
       <c r="AF87" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>647</v>
       </c>
       <c r="AG87" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>530</v>
       </c>
-      <c r="AH87" s="1"/>
+      <c r="AH87" s="1">
+        <f t="shared" si="39"/>
+        <v>416.45320000000004</v>
+      </c>
       <c r="AI87" s="1"/>
       <c r="AJ87" s="1"/>
       <c r="AK87" s="1"/>
@@ -11152,7 +11402,7 @@
         <v>2914.75</v>
       </c>
       <c r="L88" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-9.125</v>
       </c>
       <c r="M88" s="1"/>
@@ -11164,31 +11414,31 @@
         <v>1060.8110320000001</v>
       </c>
       <c r="Q88" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>581.125</v>
       </c>
       <c r="R88" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1384.7679680000001</v>
       </c>
       <c r="S88" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1764.2425930000002</v>
       </c>
       <c r="T88" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>969.53872227927945</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>794.70387072072072</v>
       </c>
       <c r="V88" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.653</v>
       </c>
       <c r="W88" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.6170910423747049</v>
       </c>
       <c r="X88" s="1">
@@ -11214,14 +11464,17 @@
       </c>
       <c r="AE88" s="1"/>
       <c r="AF88" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>970</v>
       </c>
       <c r="AG88" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>795</v>
       </c>
-      <c r="AH88" s="1"/>
+      <c r="AH88" s="1">
+        <f t="shared" si="39"/>
+        <v>581.125</v>
+      </c>
       <c r="AI88" s="1"/>
       <c r="AJ88" s="1"/>
       <c r="AK88" s="1"/>
@@ -11271,7 +11524,7 @@
         <v>2931.4</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-33.338000000000193</v>
       </c>
       <c r="M89" s="1"/>
@@ -11283,31 +11536,31 @@
         <v>706.45897599999898</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>579.61239999999998</v>
       </c>
       <c r="R89" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>1162.4198240000005</v>
       </c>
       <c r="S89" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>1540.9067212000004</v>
       </c>
       <c r="T89" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>846.80459453333367</v>
       </c>
       <c r="U89" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>694.10212666666678</v>
       </c>
       <c r="V89" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.653</v>
       </c>
       <c r="W89" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.9944876541633683</v>
       </c>
       <c r="X89" s="1">
@@ -11333,14 +11586,17 @@
       </c>
       <c r="AE89" s="1"/>
       <c r="AF89" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>847</v>
       </c>
       <c r="AG89" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>694</v>
       </c>
-      <c r="AH89" s="1"/>
+      <c r="AH89" s="1">
+        <f t="shared" si="39"/>
+        <v>579.61239999999998</v>
+      </c>
       <c r="AI89" s="1"/>
       <c r="AJ89" s="1"/>
       <c r="AK89" s="1"/>
@@ -11390,7 +11646,7 @@
         <v>2.6</v>
       </c>
       <c r="L90" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.12400000000000011</v>
       </c>
       <c r="M90" s="1"/>
@@ -11400,22 +11656,22 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.54480000000000006</v>
       </c>
       <c r="R90" s="5"/>
       <c r="S90" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T90" s="5"/>
       <c r="U90" s="5"/>
       <c r="V90" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>248.33516886930983</v>
       </c>
       <c r="W90" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>248.33516886930983</v>
       </c>
       <c r="X90" s="1">
@@ -11443,14 +11699,17 @@
         <v>105</v>
       </c>
       <c r="AF90" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG90" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH90" s="1"/>
+      <c r="AG90" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH90" s="1">
+        <f t="shared" si="39"/>
+        <v>0.54480000000000006</v>
+      </c>
       <c r="AI90" s="1"/>
       <c r="AJ90" s="1"/>
       <c r="AK90" s="1"/>
@@ -11500,7 +11759,7 @@
         <v>22.1</v>
       </c>
       <c r="L91" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0.68699999999999761</v>
       </c>
       <c r="M91" s="1"/>
@@ -11510,28 +11769,28 @@
       </c>
       <c r="P91" s="1"/>
       <c r="Q91" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>4.5573999999999995</v>
       </c>
       <c r="R91" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>17.189239999999995</v>
       </c>
       <c r="S91" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>17.189239999999995</v>
       </c>
       <c r="T91" s="5">
-        <f t="shared" ref="T91:T92" si="44">S91-U91</f>
+        <f t="shared" ref="T91:T92" si="46">S91-U91</f>
         <v>17.189239999999995</v>
       </c>
       <c r="U91" s="5"/>
       <c r="V91" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W91" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>8.2282792820467829</v>
       </c>
       <c r="X91" s="1">
@@ -11557,14 +11816,17 @@
       </c>
       <c r="AE91" s="1"/>
       <c r="AF91" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>17</v>
       </c>
       <c r="AG91" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH91" s="1"/>
+      <c r="AH91" s="1">
+        <f t="shared" si="39"/>
+        <v>4.5573999999999995</v>
+      </c>
       <c r="AI91" s="1"/>
       <c r="AJ91" s="1"/>
       <c r="AK91" s="1"/>
@@ -11614,7 +11876,7 @@
         <v>216</v>
       </c>
       <c r="L92" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-33</v>
       </c>
       <c r="M92" s="1"/>
@@ -11626,28 +11888,28 @@
         <v>116.41200000000001</v>
       </c>
       <c r="Q92" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.6</v>
       </c>
       <c r="R92" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>11.788000000000011</v>
       </c>
       <c r="S92" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>11.788000000000011</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>11.788000000000011</v>
       </c>
       <c r="U92" s="5"/>
       <c r="V92" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W92" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>11.677923497267759</v>
       </c>
       <c r="X92" s="1">
@@ -11673,14 +11935,17 @@
       </c>
       <c r="AE92" s="1"/>
       <c r="AF92" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>4</v>
       </c>
       <c r="AG92" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH92" s="1"/>
+      <c r="AH92" s="1">
+        <f t="shared" si="39"/>
+        <v>10.98</v>
+      </c>
       <c r="AI92" s="1"/>
       <c r="AJ92" s="1"/>
       <c r="AK92" s="1"/>
@@ -11732,7 +11997,7 @@
         <v>58</v>
       </c>
       <c r="L93" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>1</v>
       </c>
       <c r="M93" s="1"/>
@@ -11742,22 +12007,22 @@
       </c>
       <c r="P93" s="1"/>
       <c r="Q93" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>11.8</v>
       </c>
       <c r="R93" s="5"/>
       <c r="S93" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T93" s="5"/>
       <c r="U93" s="5"/>
       <c r="V93" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>29.745762711864405</v>
       </c>
       <c r="W93" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>29.745762711864405</v>
       </c>
       <c r="X93" s="1">
@@ -11785,14 +12050,17 @@
         <v>105</v>
       </c>
       <c r="AF93" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG93" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH93" s="1"/>
+      <c r="AG93" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH93" s="1">
+        <f t="shared" si="39"/>
+        <v>3.54</v>
+      </c>
       <c r="AI93" s="1"/>
       <c r="AJ93" s="1"/>
       <c r="AK93" s="1"/>
@@ -11842,7 +12110,7 @@
         <v>58</v>
       </c>
       <c r="L94" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-7</v>
       </c>
       <c r="M94" s="1"/>
@@ -11852,22 +12120,22 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>10.199999999999999</v>
       </c>
       <c r="R94" s="5"/>
       <c r="S94" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T94" s="5"/>
       <c r="U94" s="5"/>
       <c r="V94" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>15.19607843137255</v>
       </c>
       <c r="W94" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>15.19607843137255</v>
       </c>
       <c r="X94" s="1">
@@ -11893,14 +12161,17 @@
       </c>
       <c r="AE94" s="1"/>
       <c r="AF94" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG94" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH94" s="1"/>
+      <c r="AG94" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH94" s="1">
+        <f t="shared" si="39"/>
+        <v>0.71399999999999997</v>
+      </c>
       <c r="AI94" s="1"/>
       <c r="AJ94" s="1"/>
       <c r="AK94" s="1"/>
@@ -11950,7 +12221,7 @@
         <v>182</v>
       </c>
       <c r="L95" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="M95" s="1"/>
@@ -11960,28 +12231,28 @@
       </c>
       <c r="P95" s="1"/>
       <c r="Q95" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.200000000000003</v>
       </c>
       <c r="R95" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>132.40000000000003</v>
       </c>
       <c r="S95" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>132.40000000000003</v>
       </c>
       <c r="T95" s="5">
-        <f t="shared" ref="T95:T97" si="45">S95-U95</f>
+        <f t="shared" ref="T95:T97" si="47">S95-U95</f>
         <v>132.40000000000003</v>
       </c>
       <c r="U95" s="5"/>
       <c r="V95" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W95" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>8.3425414364640869</v>
       </c>
       <c r="X95" s="1">
@@ -12007,14 +12278,17 @@
       </c>
       <c r="AE95" s="1"/>
       <c r="AF95" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>9</v>
       </c>
       <c r="AG95" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH95" s="1"/>
+      <c r="AH95" s="1">
+        <f t="shared" si="39"/>
+        <v>2.5340000000000003</v>
+      </c>
       <c r="AI95" s="1"/>
       <c r="AJ95" s="1"/>
       <c r="AK95" s="1"/>
@@ -12064,7 +12338,7 @@
         <v>133</v>
       </c>
       <c r="L96" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="M96" s="1"/>
@@ -12076,28 +12350,28 @@
         <v>33.987999999999978</v>
       </c>
       <c r="Q96" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>26.4</v>
       </c>
       <c r="R96" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>75.811999999999955</v>
       </c>
       <c r="S96" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>75.811999999999955</v>
       </c>
       <c r="T96" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>75.811999999999955</v>
       </c>
       <c r="U96" s="5"/>
       <c r="V96" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W96" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>9.1283333333333321</v>
       </c>
       <c r="X96" s="1">
@@ -12123,14 +12397,17 @@
       </c>
       <c r="AE96" s="1"/>
       <c r="AF96" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="AG96" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH96" s="1"/>
+      <c r="AH96" s="1">
+        <f t="shared" si="39"/>
+        <v>1.8480000000000001</v>
+      </c>
       <c r="AI96" s="1"/>
       <c r="AJ96" s="1"/>
       <c r="AK96" s="1"/>
@@ -12178,7 +12455,7 @@
         <v>98</v>
       </c>
       <c r="L97" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-5</v>
       </c>
       <c r="M97" s="1"/>
@@ -12190,28 +12467,28 @@
         <v>54.053999999999988</v>
       </c>
       <c r="Q97" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>18.600000000000001</v>
       </c>
       <c r="R97" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>33.095999999999989</v>
       </c>
       <c r="S97" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>33.095999999999989</v>
       </c>
       <c r="T97" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>33.095999999999989</v>
       </c>
       <c r="U97" s="5"/>
       <c r="V97" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.999999999999998</v>
       </c>
       <c r="W97" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.220645161290321</v>
       </c>
       <c r="X97" s="1">
@@ -12237,14 +12514,17 @@
       </c>
       <c r="AE97" s="1"/>
       <c r="AF97" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>2</v>
       </c>
       <c r="AG97" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH97" s="1"/>
+      <c r="AH97" s="1">
+        <f t="shared" si="39"/>
+        <v>0.93000000000000016</v>
+      </c>
       <c r="AI97" s="1"/>
       <c r="AJ97" s="1"/>
       <c r="AK97" s="1"/>
@@ -12292,7 +12572,7 @@
         <v>29</v>
       </c>
       <c r="L98" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-13</v>
       </c>
       <c r="M98" s="1"/>
@@ -12304,24 +12584,24 @@
         <v>0</v>
       </c>
       <c r="Q98" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>3.2</v>
       </c>
       <c r="R98" s="18">
         <v>0</v>
       </c>
       <c r="S98" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T98" s="18"/>
       <c r="U98" s="18"/>
       <c r="V98" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>-0.3125</v>
       </c>
       <c r="W98" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-0.3125</v>
       </c>
       <c r="X98" s="1">
@@ -12349,14 +12629,17 @@
         <v>221</v>
       </c>
       <c r="AF98" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG98" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH98" s="1"/>
+      <c r="AG98" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH98" s="1">
+        <f t="shared" si="39"/>
+        <v>0.17600000000000002</v>
+      </c>
       <c r="AI98" s="1"/>
       <c r="AJ98" s="1"/>
       <c r="AK98" s="1"/>
@@ -12406,7 +12689,7 @@
         <v>76</v>
       </c>
       <c r="L99" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-7</v>
       </c>
       <c r="M99" s="1"/>
@@ -12418,24 +12701,24 @@
         <v>14.10399999999999</v>
       </c>
       <c r="Q99" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>13.8</v>
       </c>
       <c r="R99" s="18">
         <v>0</v>
       </c>
       <c r="S99" s="5">
-        <f t="shared" ref="S99" si="46">R99</f>
+        <f t="shared" ref="S99" si="48">R99</f>
         <v>0</v>
       </c>
       <c r="T99" s="18"/>
       <c r="U99" s="18"/>
       <c r="V99" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>10.369855072463766</v>
       </c>
       <c r="W99" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>10.369855072463766</v>
       </c>
       <c r="X99" s="1">
@@ -12463,14 +12746,17 @@
         <v>221</v>
       </c>
       <c r="AF99" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG99" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH99" s="1"/>
+      <c r="AG99" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH99" s="1">
+        <f t="shared" si="39"/>
+        <v>0.75900000000000001</v>
+      </c>
       <c r="AI99" s="1"/>
       <c r="AJ99" s="1"/>
       <c r="AK99" s="1"/>
@@ -12518,7 +12804,7 @@
         <v>4</v>
       </c>
       <c r="L100" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="M100" s="1"/>
@@ -12528,22 +12814,22 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>0.8</v>
       </c>
       <c r="R100" s="5"/>
       <c r="S100" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T100" s="5"/>
       <c r="U100" s="5"/>
       <c r="V100" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>48.75</v>
       </c>
       <c r="W100" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>48.75</v>
       </c>
       <c r="X100" s="1">
@@ -12571,14 +12857,17 @@
         <v>105</v>
       </c>
       <c r="AF100" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG100" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH100" s="1"/>
+      <c r="AG100" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH100" s="1">
+        <f t="shared" si="39"/>
+        <v>0.32000000000000006</v>
+      </c>
       <c r="AI100" s="1"/>
       <c r="AJ100" s="1"/>
       <c r="AK100" s="1"/>
@@ -12628,7 +12917,7 @@
         <v>73</v>
       </c>
       <c r="L101" s="1">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1</v>
       </c>
       <c r="M101" s="1"/>
@@ -12638,22 +12927,22 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>14.4</v>
       </c>
       <c r="R101" s="5"/>
       <c r="S101" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T101" s="5"/>
       <c r="U101" s="5"/>
       <c r="V101" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>25.500694444444441</v>
       </c>
       <c r="W101" s="1">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>25.500694444444441</v>
       </c>
       <c r="X101" s="1">
@@ -12681,14 +12970,17 @@
         <v>105</v>
       </c>
       <c r="AF101" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG101" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH101" s="1"/>
+      <c r="AG101" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH101" s="1">
+        <f t="shared" si="39"/>
+        <v>4.32</v>
+      </c>
       <c r="AI101" s="1"/>
       <c r="AJ101" s="1"/>
       <c r="AK101" s="1"/>
@@ -12738,7 +13030,7 @@
         <v>91.75</v>
       </c>
       <c r="L102" s="1">
-        <f t="shared" ref="L102:L124" si="47">E102-K102</f>
+        <f t="shared" ref="L102:L124" si="49">E102-K102</f>
         <v>17.096999999999994</v>
       </c>
       <c r="M102" s="1"/>
@@ -12748,15 +13040,15 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1">
-        <f t="shared" ref="Q102:Q124" si="48">E102/5</f>
+        <f t="shared" ref="Q102:Q124" si="50">E102/5</f>
         <v>21.769399999999997</v>
       </c>
       <c r="R102" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>140.46879999999999</v>
       </c>
       <c r="S102" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>140.46879999999999</v>
       </c>
       <c r="T102" s="5">
@@ -12765,11 +13057,11 @@
       </c>
       <c r="U102" s="5"/>
       <c r="V102" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W102" s="1">
-        <f t="shared" ref="W102:W124" si="49">(F102+O102+P102)/Q102</f>
+        <f t="shared" ref="W102:W124" si="51">(F102+O102+P102)/Q102</f>
         <v>5.5474197727084809</v>
       </c>
       <c r="X102" s="1">
@@ -12795,14 +13087,17 @@
       </c>
       <c r="AE102" s="1"/>
       <c r="AF102" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>140</v>
       </c>
       <c r="AG102" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH102" s="1"/>
+      <c r="AH102" s="1">
+        <f t="shared" si="39"/>
+        <v>21.769399999999997</v>
+      </c>
       <c r="AI102" s="1"/>
       <c r="AJ102" s="1"/>
       <c r="AK102" s="1"/>
@@ -12850,7 +13145,7 @@
         <v>13</v>
       </c>
       <c r="L103" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-2</v>
       </c>
       <c r="M103" s="1"/>
@@ -12862,22 +13157,22 @@
         <v>13.904</v>
       </c>
       <c r="Q103" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="R103" s="5"/>
       <c r="S103" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T103" s="5"/>
       <c r="U103" s="5"/>
       <c r="V103" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14.956363636363633</v>
       </c>
       <c r="W103" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>14.956363636363633</v>
       </c>
       <c r="X103" s="1">
@@ -12903,14 +13198,17 @@
       </c>
       <c r="AE103" s="1"/>
       <c r="AF103" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG103" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH103" s="1"/>
+      <c r="AG103" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH103" s="1">
+        <f t="shared" si="39"/>
+        <v>0.22000000000000003</v>
+      </c>
       <c r="AI103" s="1"/>
       <c r="AJ103" s="1"/>
       <c r="AK103" s="1"/>
@@ -12960,7 +13258,7 @@
         <v>228</v>
       </c>
       <c r="L104" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-21</v>
       </c>
       <c r="M104" s="1"/>
@@ -12972,28 +13270,28 @@
         <v>74.792000000000016</v>
       </c>
       <c r="Q104" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>41.4</v>
       </c>
       <c r="R104" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>127.26799999999992</v>
       </c>
       <c r="S104" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>127.26799999999992</v>
       </c>
       <c r="T104" s="5">
-        <f t="shared" ref="T104:T105" si="50">S104-U104</f>
+        <f t="shared" ref="T104:T105" si="52">S104-U104</f>
         <v>127.26799999999992</v>
       </c>
       <c r="U104" s="5"/>
       <c r="V104" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W104" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>8.9258937198067638</v>
       </c>
       <c r="X104" s="1">
@@ -13019,14 +13317,17 @@
       </c>
       <c r="AE104" s="1"/>
       <c r="AF104" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>10</v>
       </c>
       <c r="AG104" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH104" s="1"/>
+      <c r="AH104" s="1">
+        <f t="shared" si="39"/>
+        <v>3.3119999999999998</v>
+      </c>
       <c r="AI104" s="1"/>
       <c r="AJ104" s="1"/>
       <c r="AK104" s="1"/>
@@ -13076,7 +13377,7 @@
         <v>157</v>
       </c>
       <c r="L105" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-4</v>
       </c>
       <c r="M105" s="1"/>
@@ -13088,28 +13389,28 @@
         <v>48.036000000000008</v>
       </c>
       <c r="Q105" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>30.6</v>
       </c>
       <c r="R105" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>144.16400000000004</v>
       </c>
       <c r="S105" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>144.16400000000004</v>
       </c>
       <c r="T105" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>144.16400000000004</v>
       </c>
       <c r="U105" s="5"/>
       <c r="V105" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.000000000000002</v>
       </c>
       <c r="W105" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>7.2887581699346402</v>
       </c>
       <c r="X105" s="1">
@@ -13135,14 +13436,17 @@
       </c>
       <c r="AE105" s="1"/>
       <c r="AF105" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>12</v>
       </c>
       <c r="AG105" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH105" s="1"/>
+      <c r="AH105" s="1">
+        <f t="shared" si="39"/>
+        <v>2.448</v>
+      </c>
       <c r="AI105" s="1"/>
       <c r="AJ105" s="1"/>
       <c r="AK105" s="1"/>
@@ -13190,7 +13494,7 @@
         <v>20</v>
       </c>
       <c r="L106" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-10</v>
       </c>
       <c r="M106" s="1"/>
@@ -13202,22 +13506,22 @@
         <v>19.66</v>
       </c>
       <c r="Q106" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>2</v>
       </c>
       <c r="R106" s="5"/>
       <c r="S106" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T106" s="5"/>
       <c r="U106" s="5"/>
       <c r="V106" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.33</v>
       </c>
       <c r="W106" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.33</v>
       </c>
       <c r="X106" s="1">
@@ -13243,14 +13547,17 @@
       </c>
       <c r="AE106" s="1"/>
       <c r="AF106" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG106" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH106" s="1"/>
+      <c r="AG106" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH106" s="1">
+        <f t="shared" si="39"/>
+        <v>0.34</v>
+      </c>
       <c r="AI106" s="1"/>
       <c r="AJ106" s="1"/>
       <c r="AK106" s="1"/>
@@ -13300,7 +13607,7 @@
         <v>341.3</v>
       </c>
       <c r="L107" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.14099999999996271</v>
       </c>
       <c r="M107" s="1"/>
@@ -13312,15 +13619,15 @@
         <v>217.13247600000011</v>
       </c>
       <c r="Q107" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>68.288199999999989</v>
       </c>
       <c r="R107" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>97.595923999999741</v>
       </c>
       <c r="S107" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>97.595923999999741</v>
       </c>
       <c r="T107" s="5">
@@ -13329,11 +13636,11 @@
       </c>
       <c r="U107" s="5"/>
       <c r="V107" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W107" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>10.570823011881998</v>
       </c>
       <c r="X107" s="1">
@@ -13359,14 +13666,17 @@
       </c>
       <c r="AE107" s="1"/>
       <c r="AF107" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>98</v>
       </c>
       <c r="AG107" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH107" s="1"/>
+      <c r="AH107" s="1">
+        <f t="shared" si="39"/>
+        <v>68.288199999999989</v>
+      </c>
       <c r="AI107" s="1"/>
       <c r="AJ107" s="1"/>
       <c r="AK107" s="1"/>
@@ -13416,7 +13726,7 @@
         <v>194.1</v>
       </c>
       <c r="L108" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>6.6529999999999916</v>
       </c>
       <c r="M108" s="1"/>
@@ -13426,22 +13736,22 @@
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>40.150599999999997</v>
       </c>
       <c r="R108" s="5"/>
       <c r="S108" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T108" s="5"/>
       <c r="U108" s="5"/>
       <c r="V108" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>14.14384841073359</v>
       </c>
       <c r="W108" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>14.14384841073359</v>
       </c>
       <c r="X108" s="1">
@@ -13467,14 +13777,17 @@
       </c>
       <c r="AE108" s="1"/>
       <c r="AF108" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG108" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH108" s="1"/>
+      <c r="AG108" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH108" s="1">
+        <f t="shared" si="39"/>
+        <v>40.150599999999997</v>
+      </c>
       <c r="AI108" s="1"/>
       <c r="AJ108" s="1"/>
       <c r="AK108" s="1"/>
@@ -13524,7 +13837,7 @@
         <v>429.42</v>
       </c>
       <c r="L109" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-3.2100000000000364</v>
       </c>
       <c r="M109" s="1"/>
@@ -13536,22 +13849,22 @@
         <v>92.485420000000033</v>
       </c>
       <c r="Q109" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>85.24199999999999</v>
       </c>
       <c r="R109" s="5"/>
       <c r="S109" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T109" s="5"/>
       <c r="U109" s="5"/>
       <c r="V109" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.366072827948665</v>
       </c>
       <c r="W109" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>12.366072827948665</v>
       </c>
       <c r="X109" s="1">
@@ -13577,14 +13890,17 @@
       </c>
       <c r="AE109" s="1"/>
       <c r="AF109" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG109" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH109" s="1"/>
+      <c r="AG109" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH109" s="1">
+        <f t="shared" si="39"/>
+        <v>85.24199999999999</v>
+      </c>
       <c r="AI109" s="1"/>
       <c r="AJ109" s="1"/>
       <c r="AK109" s="1"/>
@@ -13632,7 +13948,7 @@
         <v>2.6</v>
       </c>
       <c r="L110" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0.21799999999999997</v>
       </c>
       <c r="M110" s="1"/>
@@ -13642,22 +13958,22 @@
       </c>
       <c r="P110" s="1"/>
       <c r="Q110" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0.56359999999999999</v>
       </c>
       <c r="R110" s="5"/>
       <c r="S110" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T110" s="5"/>
       <c r="U110" s="5"/>
       <c r="V110" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.753016323633782</v>
       </c>
       <c r="W110" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.753016323633782</v>
       </c>
       <c r="X110" s="1">
@@ -13685,14 +14001,17 @@
         <v>246</v>
       </c>
       <c r="AF110" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG110" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH110" s="1"/>
+      <c r="AG110" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH110" s="1">
+        <f t="shared" si="39"/>
+        <v>0.56359999999999999</v>
+      </c>
       <c r="AI110" s="1"/>
       <c r="AJ110" s="1"/>
       <c r="AK110" s="1"/>
@@ -13742,7 +14061,7 @@
         <v>343</v>
       </c>
       <c r="L111" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-16</v>
       </c>
       <c r="M111" s="1"/>
@@ -13754,15 +14073,15 @@
         <v>162.77599999999981</v>
       </c>
       <c r="Q111" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>65.400000000000006</v>
       </c>
       <c r="R111" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>112.64400000000012</v>
       </c>
       <c r="S111" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>112.64400000000012</v>
       </c>
       <c r="T111" s="5">
@@ -13771,11 +14090,11 @@
       </c>
       <c r="U111" s="5"/>
       <c r="V111" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W111" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>10.277614678899081</v>
       </c>
       <c r="X111" s="1">
@@ -13803,14 +14122,17 @@
         <v>249</v>
       </c>
       <c r="AF111" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>32</v>
       </c>
       <c r="AG111" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH111" s="1"/>
+      <c r="AH111" s="1">
+        <f t="shared" si="39"/>
+        <v>18.312000000000005</v>
+      </c>
       <c r="AI111" s="1"/>
       <c r="AJ111" s="1"/>
       <c r="AK111" s="1"/>
@@ -13860,7 +14182,7 @@
         <v>316</v>
       </c>
       <c r="L112" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-21</v>
       </c>
       <c r="M112" s="1"/>
@@ -13872,22 +14194,22 @@
         <v>122.3719999999998</v>
       </c>
       <c r="Q112" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>59</v>
       </c>
       <c r="R112" s="5"/>
       <c r="S112" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T112" s="5"/>
       <c r="U112" s="5"/>
       <c r="V112" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.005966101694915</v>
       </c>
       <c r="W112" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>12.005966101694915</v>
       </c>
       <c r="X112" s="1">
@@ -13915,14 +14237,17 @@
         <v>249</v>
       </c>
       <c r="AF112" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG112" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH112" s="1"/>
+      <c r="AG112" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH112" s="1">
+        <f t="shared" si="39"/>
+        <v>16.520000000000003</v>
+      </c>
       <c r="AI112" s="1"/>
       <c r="AJ112" s="1"/>
       <c r="AK112" s="1"/>
@@ -13972,7 +14297,7 @@
         <v>207.2</v>
       </c>
       <c r="L113" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-2.23599999999999</v>
       </c>
       <c r="M113" s="1"/>
@@ -13984,15 +14309,15 @@
         <v>170.49342799999999</v>
       </c>
       <c r="Q113" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>40.992800000000003</v>
       </c>
       <c r="R113" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>38.556172000000061</v>
       </c>
       <c r="S113" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>38.556172000000061</v>
       </c>
       <c r="T113" s="5">
@@ -14001,11 +14326,11 @@
       </c>
       <c r="U113" s="5"/>
       <c r="V113" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W113" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.059440389531819</v>
       </c>
       <c r="X113" s="1">
@@ -14031,14 +14356,17 @@
       </c>
       <c r="AE113" s="1"/>
       <c r="AF113" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>39</v>
       </c>
       <c r="AG113" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH113" s="1"/>
+      <c r="AH113" s="1">
+        <f t="shared" si="39"/>
+        <v>40.992800000000003</v>
+      </c>
       <c r="AI113" s="1"/>
       <c r="AJ113" s="1"/>
       <c r="AK113" s="1"/>
@@ -14088,7 +14416,7 @@
         <v>75</v>
       </c>
       <c r="L114" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1.7810000000000059</v>
       </c>
       <c r="M114" s="1"/>
@@ -14098,22 +14426,22 @@
       </c>
       <c r="P114" s="1"/>
       <c r="Q114" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>14.643799999999999</v>
       </c>
       <c r="R114" s="5"/>
       <c r="S114" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T114" s="5"/>
       <c r="U114" s="5"/>
       <c r="V114" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>28.901856075608794</v>
       </c>
       <c r="W114" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>28.901856075608794</v>
       </c>
       <c r="X114" s="1">
@@ -14141,14 +14469,17 @@
         <v>105</v>
       </c>
       <c r="AF114" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG114" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH114" s="1"/>
+      <c r="AG114" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH114" s="1">
+        <f t="shared" si="39"/>
+        <v>14.643799999999999</v>
+      </c>
       <c r="AI114" s="1"/>
       <c r="AJ114" s="1"/>
       <c r="AK114" s="1"/>
@@ -14198,7 +14529,7 @@
         <v>272.18299999999999</v>
       </c>
       <c r="L115" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>14.381000000000029</v>
       </c>
       <c r="M115" s="1"/>
@@ -14208,15 +14539,15 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>57.312800000000003</v>
       </c>
       <c r="R115" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>46.488600000000019</v>
       </c>
       <c r="S115" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>46.488600000000019</v>
       </c>
       <c r="T115" s="5">
@@ -14225,11 +14556,11 @@
       </c>
       <c r="U115" s="5"/>
       <c r="V115" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W115" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.188861824932649</v>
       </c>
       <c r="X115" s="1">
@@ -14255,14 +14586,17 @@
       </c>
       <c r="AE115" s="1"/>
       <c r="AF115" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>46</v>
       </c>
       <c r="AG115" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH115" s="1"/>
+      <c r="AH115" s="1">
+        <f t="shared" si="39"/>
+        <v>57.312800000000003</v>
+      </c>
       <c r="AI115" s="1"/>
       <c r="AJ115" s="1"/>
       <c r="AK115" s="1"/>
@@ -14312,7 +14646,7 @@
         <v>362</v>
       </c>
       <c r="L116" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>16.274999999999977</v>
       </c>
       <c r="M116" s="1"/>
@@ -14322,22 +14656,22 @@
       </c>
       <c r="P116" s="1"/>
       <c r="Q116" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>75.655000000000001</v>
       </c>
       <c r="R116" s="5"/>
       <c r="S116" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T116" s="5"/>
       <c r="U116" s="5"/>
       <c r="V116" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12.556605644042033</v>
       </c>
       <c r="W116" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>12.556605644042033</v>
       </c>
       <c r="X116" s="1">
@@ -14365,14 +14699,17 @@
         <v>249</v>
       </c>
       <c r="AF116" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG116" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH116" s="1"/>
+      <c r="AG116" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH116" s="1">
+        <f t="shared" si="39"/>
+        <v>75.655000000000001</v>
+      </c>
       <c r="AI116" s="1"/>
       <c r="AJ116" s="1"/>
       <c r="AK116" s="1"/>
@@ -14422,7 +14759,7 @@
         <v>119.1</v>
       </c>
       <c r="L117" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>6.5100000000000051</v>
       </c>
       <c r="M117" s="1"/>
@@ -14434,15 +14771,15 @@
         <v>24.319771999999979</v>
       </c>
       <c r="Q117" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>25.122</v>
       </c>
       <c r="R117" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>5.443587999999977</v>
       </c>
       <c r="S117" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.443587999999977</v>
       </c>
       <c r="T117" s="5">
@@ -14451,11 +14788,11 @@
       </c>
       <c r="U117" s="5"/>
       <c r="V117" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W117" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.783313908128335</v>
       </c>
       <c r="X117" s="1">
@@ -14483,14 +14820,17 @@
         <v>249</v>
       </c>
       <c r="AF117" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>5</v>
       </c>
       <c r="AG117" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH117" s="1"/>
+      <c r="AH117" s="1">
+        <f t="shared" si="39"/>
+        <v>25.122</v>
+      </c>
       <c r="AI117" s="1"/>
       <c r="AJ117" s="1"/>
       <c r="AK117" s="1"/>
@@ -14542,7 +14882,7 @@
         <v>273.35000000000002</v>
       </c>
       <c r="L118" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-25.478000000000009</v>
       </c>
       <c r="M118" s="1"/>
@@ -14552,22 +14892,22 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>49.574400000000004</v>
       </c>
       <c r="R118" s="5"/>
       <c r="S118" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T118" s="5"/>
       <c r="U118" s="5"/>
       <c r="V118" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>35.424352084947067</v>
       </c>
       <c r="W118" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>35.424352084947067</v>
       </c>
       <c r="X118" s="1">
@@ -14595,14 +14935,17 @@
         <v>275</v>
       </c>
       <c r="AF118" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG118" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH118" s="1"/>
+      <c r="AG118" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH118" s="1">
+        <f t="shared" si="39"/>
+        <v>49.574400000000004</v>
+      </c>
       <c r="AI118" s="1"/>
       <c r="AJ118" s="1"/>
       <c r="AK118" s="1"/>
@@ -14652,7 +14995,7 @@
         <v>353</v>
       </c>
       <c r="L119" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-15</v>
       </c>
       <c r="M119" s="1"/>
@@ -14664,28 +15007,28 @@
         <v>170.208</v>
       </c>
       <c r="Q119" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>67.599999999999994</v>
       </c>
       <c r="R119" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>120.3119999999999</v>
       </c>
       <c r="S119" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>120.3119999999999</v>
       </c>
       <c r="T119" s="5">
-        <f t="shared" ref="T119:T122" si="51">S119-U119</f>
+        <f t="shared" ref="T119:T122" si="53">S119-U119</f>
         <v>120.3119999999999</v>
       </c>
       <c r="U119" s="5"/>
       <c r="V119" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W119" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>10.220236686390534</v>
       </c>
       <c r="X119" s="1">
@@ -14711,14 +15054,17 @@
       </c>
       <c r="AE119" s="1"/>
       <c r="AF119" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>36</v>
       </c>
       <c r="AG119" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH119" s="1"/>
+      <c r="AH119" s="1">
+        <f t="shared" si="39"/>
+        <v>20.279999999999998</v>
+      </c>
       <c r="AI119" s="1"/>
       <c r="AJ119" s="1"/>
       <c r="AK119" s="1"/>
@@ -14768,7 +15114,7 @@
         <v>284</v>
       </c>
       <c r="L120" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-21</v>
       </c>
       <c r="M120" s="1"/>
@@ -14780,28 +15126,28 @@
         <v>125.3900000000001</v>
       </c>
       <c r="Q120" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>52.6</v>
       </c>
       <c r="R120" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>43.000000000000057</v>
       </c>
       <c r="S120" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>43.000000000000057</v>
       </c>
       <c r="T120" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>43.000000000000057</v>
       </c>
       <c r="U120" s="5"/>
       <c r="V120" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W120" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.182509505703422</v>
       </c>
       <c r="X120" s="1">
@@ -14827,14 +15173,17 @@
       </c>
       <c r="AE120" s="1"/>
       <c r="AF120" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>13</v>
       </c>
       <c r="AG120" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH120" s="1"/>
+      <c r="AH120" s="1">
+        <f t="shared" si="39"/>
+        <v>15.78</v>
+      </c>
       <c r="AI120" s="1"/>
       <c r="AJ120" s="1"/>
       <c r="AK120" s="1"/>
@@ -14884,7 +15233,7 @@
         <v>293.75</v>
       </c>
       <c r="L121" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>5.9289999999999736</v>
       </c>
       <c r="M121" s="1"/>
@@ -14896,28 +15245,28 @@
         <v>29.343119999999988</v>
       </c>
       <c r="Q121" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>59.935799999999993</v>
       </c>
       <c r="R121" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>394.06237399999986</v>
       </c>
       <c r="S121" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>394.06237399999986</v>
       </c>
       <c r="T121" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>394.06237399999986</v>
       </c>
       <c r="U121" s="5"/>
       <c r="V121" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W121" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>5.4252587935757939</v>
       </c>
       <c r="X121" s="1">
@@ -14943,14 +15292,17 @@
       </c>
       <c r="AE121" s="1"/>
       <c r="AF121" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>394</v>
       </c>
       <c r="AG121" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0</v>
       </c>
-      <c r="AH121" s="1"/>
+      <c r="AH121" s="1">
+        <f t="shared" si="39"/>
+        <v>59.935799999999993</v>
+      </c>
       <c r="AI121" s="1"/>
       <c r="AJ121" s="1"/>
       <c r="AK121" s="1"/>
@@ -15000,7 +15352,7 @@
         <v>317</v>
       </c>
       <c r="L122" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-17</v>
       </c>
       <c r="M122" s="1"/>
@@ -15012,19 +15364,19 @@
         <v>120.47800000000009</v>
       </c>
       <c r="Q122" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>60</v>
       </c>
       <c r="R122" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>459.52199999999993</v>
       </c>
       <c r="S122" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>459.52199999999993</v>
       </c>
       <c r="T122" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>252.5301081081081</v>
       </c>
       <c r="U122" s="5">
@@ -15032,11 +15384,11 @@
         <v>206.99189189189184</v>
       </c>
       <c r="V122" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>12</v>
       </c>
       <c r="W122" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>4.3413000000000013</v>
       </c>
       <c r="X122" s="1">
@@ -15062,14 +15414,17 @@
       </c>
       <c r="AE122" s="1"/>
       <c r="AF122" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>76</v>
       </c>
       <c r="AG122" s="1">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>62</v>
       </c>
-      <c r="AH122" s="1"/>
+      <c r="AH122" s="1">
+        <f t="shared" si="39"/>
+        <v>18</v>
+      </c>
       <c r="AI122" s="1"/>
       <c r="AJ122" s="1"/>
       <c r="AK122" s="1"/>
@@ -15119,7 +15474,7 @@
         <v>47</v>
       </c>
       <c r="L123" s="1">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-17</v>
       </c>
       <c r="M123" s="1"/>
@@ -15129,22 +15484,22 @@
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>6</v>
       </c>
       <c r="R123" s="5"/>
       <c r="S123" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T123" s="5"/>
       <c r="U123" s="5"/>
       <c r="V123" s="1">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>11.666666666666666</v>
       </c>
       <c r="W123" s="1">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>11.666666666666666</v>
       </c>
       <c r="X123" s="1">
@@ -15170,14 +15525,17 @@
       </c>
       <c r="AE123" s="1"/>
       <c r="AF123" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG123" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH123" s="1"/>
+      <c r="AG123" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH123" s="1">
+        <f t="shared" si="39"/>
+        <v>0.72</v>
+      </c>
       <c r="AI123" s="1"/>
       <c r="AJ123" s="1"/>
       <c r="AK123" s="1"/>
@@ -15221,7 +15579,7 @@
       <c r="J124" s="9"/>
       <c r="K124" s="9"/>
       <c r="L124" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="M124" s="9"/>
@@ -15231,22 +15589,22 @@
       </c>
       <c r="P124" s="9"/>
       <c r="Q124" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="R124" s="11"/>
       <c r="S124" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="T124" s="11"/>
       <c r="U124" s="11"/>
       <c r="V124" s="1" t="e">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>#DIV/0!</v>
       </c>
       <c r="W124" s="9" t="e">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>#DIV/0!</v>
       </c>
       <c r="X124" s="9">
@@ -15272,14 +15630,17 @@
       </c>
       <c r="AE124" s="9"/>
       <c r="AF124" s="1">
-        <f t="shared" si="36"/>
-        <v>0</v>
-      </c>
-      <c r="AG124" s="1">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="AH124" s="1"/>
+      <c r="AG124" s="1">
+        <f t="shared" si="38"/>
+        <v>0</v>
+      </c>
+      <c r="AH124" s="1">
+        <f t="shared" si="39"/>
+        <v>0</v>
+      </c>
       <c r="AI124" s="1"/>
       <c r="AJ124" s="1"/>
       <c r="AK124" s="1"/>
